--- a/app/exports/prime_castings.xlsx
+++ b/app/exports/prime_castings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J142"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,26 +433,26 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2">
-        <v>1673192</v>
+        <v>1673263</v>
       </c>
       <c r="B2" t="str">
-        <v>The Great Christmas Light Fight Competition on ABC</v>
+        <v>Casting for Deception Game Reality Show</v>
       </c>
       <c r="C2" t="str">
-        <v>50000.00/ event</v>
+        <v>99999.99/ event</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">"The Great Christmas Light Fight" is casting for Season 14, seeking families/communities with exceptional, unique, and passionate Christmas light displays. Apply at lightfightcasting.com for a chance to win $50,000 and showcase your holiday magic. Displays should be more than typical neighborhood lights.
+        <v xml:space="preserve">Deception Game seeks contestants (18+) skilled in lying and scheming. Players will bluff their way to the top for a grand prize.
 </v>
       </c>
       <c r="E2" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F2" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G2" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673192/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673263/edit</v>
       </c>
       <c r="H2" t="str">
         <v>07/04/2025</v>
@@ -461,120 +461,120 @@
         <v>Nationwide</v>
       </c>
       <c r="J2" t="str">
-        <v>https://www.exploretalent.com/auditions/1673192</v>
+        <v>https://www.exploretalent.com/auditions/1673263</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3">
-        <v>1673159</v>
+        <v>1673231</v>
       </c>
       <c r="B3" t="str">
-        <v>Executive Assistant to Director</v>
+        <v>Casting Call for The Apprentice UK, 2025</v>
       </c>
       <c r="C3" t="str">
-        <v>28000.00/ event</v>
+        <v>99999.99/ event</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">A casting agency seeks an organized Executive Assistant to support a director and team. Responsibilities include HR, scheduling, database management, contract administration, client communication, and office operations. The role requires professionalism, attention to detail, and the ability to thrive in a fast-paced environment.
+        <v xml:space="preserve">Apply for The Apprentice UK! Face business challenges, showcase your skills, and compete for a substantial investment and partnership with Lord Sugar. This show has launched many successful UK entrepreneurs.
 </v>
       </c>
       <c r="E3" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F3" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G3" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673159/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673231/edit</v>
       </c>
       <c r="H3" t="str">
-        <v>07/03/2025</v>
+        <v>01/11/2026</v>
       </c>
       <c r="I3" t="str">
-        <v>London, United Kingdom</v>
+        <v>UK</v>
       </c>
       <c r="J3" t="str">
-        <v>https://www.exploretalent.com/auditions/1673159</v>
+        <v>https://www.exploretalent.com/auditions/1673231</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4">
-        <v>1673181</v>
+        <v>1673229</v>
       </c>
       <c r="B4" t="str">
-        <v>Dipping Sauce Commercial Casting Call for Chicken Tender Loving Couples</v>
+        <v>Casting Call for FOX's The Floor</v>
       </c>
       <c r="C4" t="str">
-        <v>13500.00/ event</v>
+        <v>99999.99/ event</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Engaged or soon-to-be-married couples who adore chicken tenders can get legally married in Las Vegas by the brand's mascot in a commercial campaign celebrating love and their favorite food.
+        <v xml:space="preserve">Compete on FOX's "The Floor," hosted by Rob Lowe! 81 contestants battle in trivia duels on a massive grid, vying to conquer the entire floor. Created by John de Mol, this high-stakes quiz show offers a grand prize to the ultimate trivia champion.
 </v>
       </c>
       <c r="E4" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F4" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G4" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673181/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673229/edit</v>
       </c>
       <c r="H4" t="str">
-        <v>07/03/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I4" t="str">
-        <v>Las Vegas</v>
+        <v>Nationwide</v>
       </c>
       <c r="J4" t="str">
-        <v>https://www.exploretalent.com/auditions/1673181</v>
+        <v>https://www.exploretalent.com/auditions/1673229</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5">
-        <v>1673180</v>
+        <v>1673266</v>
       </c>
       <c r="B5" t="str">
-        <v>Major Clothing Brand Commercial Casting Call</v>
+        <v>Casting Call for Fear Factor Reboot</v>
       </c>
       <c r="C5" t="str">
-        <v>13000.00/ event</v>
+        <v>50000.00/ event</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Paid commercial seeks diverse dancers of all ages/genders/body types for a global clothing brand campaign. Showcase your individuality, energy, and style through choreographed and freestyle dance. Collaborate with creatives and represent the brand with enthusiasm and rhythm.
+        <v xml:space="preserve">Fear Factor is back! Casting is open for fearless contestants (18+) to live together and face extreme physical and mental challenges. Producers seek bold individuals ready to prove fear is not a factor in this intense reality competition.
 </v>
       </c>
       <c r="E5" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F5" t="str">
         <v>Any</v>
       </c>
       <c r="G5" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673180/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673266/edit</v>
       </c>
       <c r="H5" t="str">
-        <v>06/13/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>U.S. and Canada</v>
       </c>
       <c r="J5" t="str">
-        <v>https://www.exploretalent.com/auditions/1673180</v>
+        <v>https://www.exploretalent.com/auditions/1673266</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6">
-        <v>1672323</v>
+        <v>1673192</v>
       </c>
       <c r="B6" t="str">
-        <v>Mobile Phone Commercial Casting Call for Mia – Female Lead Opportunity</v>
+        <v>The Great Christmas Light Fight Competition on ABC</v>
       </c>
       <c r="C6" t="str">
-        <v>12000.00/ event</v>
+        <v>50000.00/ event</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a female actor (20-25, any ethnicity) with strong English skills for "Mia" in a mobile phone commercial. Requires subtle expressions, natural line delivery, and comfort with video/photo shoots. Must have a valid passport. Bangkok shoot with premium compensation.
+        <v xml:space="preserve">Apply for Season 14 of ABC's "The Great Christmas Light Fight"! Families/communities with spectacular, creative Christmas light displays featuring massive lights, intricate designs, synchronized music, and animation are encouraged to showcase their holiday spirit.
 </v>
       </c>
       <c r="E6" t="str">
@@ -584,789 +584,789 @@
         <v>Any</v>
       </c>
       <c r="G6" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672323/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673192/edit</v>
       </c>
       <c r="H6" t="str">
-        <v>06/27/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I6" t="str">
-        <v>N/A</v>
+        <v>Nationwide</v>
       </c>
       <c r="J6" t="str">
-        <v>https://www.exploretalent.com/auditions/1672323</v>
+        <v>https://www.exploretalent.com/auditions/1673192</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7">
-        <v>1672537</v>
+        <v>1673759</v>
       </c>
       <c r="B7" t="str">
-        <v>Pharmaceutical Commercial Casting for South Korean Families and Seniors</v>
+        <v>Mercury Home Experience Campaign Casting</v>
       </c>
       <c r="C7" t="str">
-        <v>12000.00/ event</v>
+        <v>15000.00/ event</v>
       </c>
       <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">South Korean families, couples, and seniors are needed for a paid pharmaceutical commercial. Participants with authentic cultural backgrounds will be flown to Toronto (travel/accommodation provided) for a mid-June shoot. The nationally visible campaign seeks individuals available for one or more days.
+        <v xml:space="preserve">Mercury is casting real customer families for a commercial celebrating resilience and humor. The in-home shoot will feature an immersive light and sound experience, showcasing your family's unique stories. No acting experience needed – just be yourselves and share a memorable household moment.
 </v>
       </c>
       <c r="E7" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F7" t="str">
         <v>Any</v>
       </c>
       <c r="G7" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672537/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673759/edit</v>
       </c>
       <c r="H7" t="str">
-        <v>06/21/2025</v>
+        <v>07/10/2025</v>
       </c>
       <c r="I7" t="str">
-        <v>Canada</v>
+        <v>Auckland, New Zealand</v>
       </c>
       <c r="J7" t="str">
-        <v>https://www.exploretalent.com/auditions/1672537</v>
+        <v>https://www.exploretalent.com/auditions/1673759</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8">
-        <v>1672325</v>
+        <v>1673181</v>
       </c>
       <c r="B8" t="str">
-        <v>Mobile Phone Commercial Casting Call for Lead Role Kai</v>
+        <v>Dipping Sauce Commercial Casting Call for Chicken Tender Loving Couples</v>
       </c>
       <c r="C8" t="str">
-        <v>12000.00/ event</v>
+        <v>13500.00/ event</v>
       </c>
       <c r="D8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Global mobile phone campaign seeks a confident, English-speaking young man ("Kai") for lead role. Bangkok shoot includes video/photo. Great exposure for emerging talent. Acting experience preferred. All ethnicities welcome. Compensation includes fees and buyout (agency fees apply).
+        <v xml:space="preserve">A commercial campaign seeks real, engaged couples passionate about chicken tenders to get legally married in Las Vegas, officiated by the brand's mascot. The commercial aims to capture authentic love stories and enthusiasm for chicken tenders on screen.
 </v>
       </c>
       <c r="E8" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F8" t="str">
         <v>Any</v>
       </c>
       <c r="G8" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672325/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673181/edit</v>
       </c>
       <c r="H8" t="str">
-        <v>06/27/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="I8" t="str">
-        <v>N/A</v>
+        <v>Las Vegas</v>
       </c>
       <c r="J8" t="str">
-        <v>https://www.exploretalent.com/auditions/1672325</v>
+        <v>https://www.exploretalent.com/auditions/1673181</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9">
-        <v>1672490</v>
+        <v>1672323</v>
       </c>
       <c r="B9" t="str">
-        <v>eGift Card Platform Holiday Family Commercial Casting Call</v>
+        <v>Mobile Phone Commercial Casting Call for Mia – Female Lead Opportunity</v>
       </c>
       <c r="C9" t="str">
-        <v>11000.00/ event</v>
+        <v>12000.00/ event</v>
       </c>
       <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">An eGift card brand seeks a real, energetic family of four (parents 38-48, teens 15-17, any ethnicity) for a one-day shoot. They'll portray cheerful carolers, emphasizing genuine connection and holiday joy. No acting experience needed, but camera confidence is a must.
+        <v xml:space="preserve">Seeking a 20-25 year old woman ("Mia") for a global mobile phone commercial. Must be intellectually curious, detail-oriented, and able to convey subtle, thoughtful expressions. Open to all ethnicities. Shoot in Bangkok.
 </v>
       </c>
       <c r="E9" t="str">
-        <v>1 - 80</v>
+        <v>20 - 25</v>
       </c>
       <c r="F9" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G9" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672490/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672323/edit</v>
       </c>
       <c r="H9" t="str">
-        <v>06/22/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="I9" t="str">
-        <v>Sydney, Australia</v>
+        <v>N/A</v>
       </c>
       <c r="J9" t="str">
-        <v>https://www.exploretalent.com/auditions/1672490</v>
+        <v>https://www.exploretalent.com/auditions/1672323</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10">
-        <v>1673116</v>
+        <v>1672325</v>
       </c>
       <c r="B10" t="str">
-        <v>How To Get on GSN's Game Show Split Second – Online Audition</v>
+        <v>Mobile Phone Commercial Casting Call for Lead Role Kai</v>
       </c>
       <c r="C10" t="str">
-        <v>10000.00/ negotiable</v>
+        <v>12000.00/ event</v>
       </c>
       <c r="D10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Trivia buffs can apply to be on "Split Second," a rebooted game show hosted by Michael Higgins. Contestants answer general interest questions in a fast-paced competition. Quick responses and accuracy are key to advancing to the bonus round for a chance to win $10,000. Apply via the casting notice or GSN's website.
+        <v xml:space="preserve">A global mobile phone campaign seeks a dynamic male actor for the lead role of "Kai." The project, filming in Bangkok, requires a confident and free-spirited young man. This is a great opportunity for emerging talent seeking international exposure.
 </v>
       </c>
       <c r="E10" t="str">
-        <v>1 - 80</v>
+        <v>1 - 3</v>
       </c>
       <c r="F10" t="str">
         <v>Any</v>
       </c>
       <c r="G10" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673116/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672325/edit</v>
       </c>
       <c r="H10" t="str">
-        <v>07/03/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="I10" t="str">
-        <v>Los Angeles</v>
+        <v>N/A</v>
       </c>
       <c r="J10" t="str">
-        <v>https://www.exploretalent.com/auditions/1673116</v>
+        <v>https://www.exploretalent.com/auditions/1672325</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11">
-        <v>1672043</v>
+        <v>1674077</v>
       </c>
       <c r="B11" t="str">
-        <v>Canada - Breast Cancer Medication Commercial, $9000</v>
+        <v>Medical App Commercial Casting</v>
       </c>
       <c r="C11" t="str">
-        <v>9000.00/ n/a</v>
+        <v>10000.00/ event</v>
       </c>
       <c r="D11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Casting call for women in the US or Canada who have experienced breast cancer (diagnosis, surgeries, recovery) to share their stories in a commercial for a breast cancer medication. Filming is in Canada between June 18-25 (travel, rehearsal, and 2-3 filming days). Total compensation is $9k with buyout, and travel expenses are covered. Must have a valid passport. Submit recent photos, full name, age, phone number, and a brief (50 words max) description of surgeries.
+        <v xml:space="preserve">Twins (male/female, ages 3-80, all ethnicities) are wanted for an international commercial for a leading medical app. This is a paid opportunity to work together on-camera, promoting healthcare technology in various shoot environments.
 </v>
       </c>
       <c r="E11" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F11" t="str">
         <v>Any</v>
       </c>
       <c r="G11" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672043/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674077/edit</v>
       </c>
       <c r="H11" t="str">
-        <v>06/05/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="I11" t="str">
-        <v>Miami, FL&gt;Orlando, FL&gt;Tampa, FL</v>
+        <v>N/A</v>
       </c>
       <c r="J11" t="str">
-        <v>https://www.exploretalent.com/auditions/1672043</v>
+        <v>https://www.exploretalent.com/auditions/1674077</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12">
-        <v>1673085</v>
+        <v>1673651</v>
       </c>
       <c r="B12" t="str">
-        <v>Airlines Commercial Los Angeles Casting Call for Asian Women</v>
+        <v>Commercial Casting Call for Canadian Business Owners</v>
       </c>
       <c r="C12" t="str">
-        <v>7500.00/ event</v>
+        <v>10000.00/ event</v>
       </c>
       <c r="D12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Los Angeles casting call for Asian women, ages 35-40, for an airline commercial. Seeking professional, local talent available for a fitting and potential overnight shoot. Represents real airline passengers in a structured, on-set environment. Travel not covered.
+        <v xml:space="preserve">Canadian business owners wanted! Share your story and business on a national platform. Selected participants will be filmed, interviewed, and represent their industry with authenticity and pride.
 </v>
       </c>
       <c r="E12" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F12" t="str">
         <v>Any</v>
       </c>
       <c r="G12" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673085/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673651/edit</v>
       </c>
       <c r="H12" t="str">
-        <v>06/09/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I12" t="str">
-        <v>Los Angeles</v>
+        <v>Canada</v>
       </c>
       <c r="J12" t="str">
-        <v>https://www.exploretalent.com/auditions/1673085</v>
+        <v>https://www.exploretalent.com/auditions/1673651</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13">
-        <v>1673084</v>
+        <v>1674426</v>
       </c>
       <c r="B13" t="str">
-        <v>Airlines Commercial Casting Call for African American Women</v>
+        <v>Sydney Weight Loss Campaign Casting</v>
       </c>
       <c r="C13" t="str">
-        <v>7500.00/ event</v>
+        <v>8800.00/ event</v>
       </c>
       <c r="D13" t="str" xml:space="preserve">
-        <v xml:space="preserve">National airline commercial seeks relatable, confident African American women (35-40) for a high-paying, non-union shoot. Local talent only; must attend a fitting and be available for potential overnight filming. Portray an authentic passenger, following on-set direction.
+        <v xml:space="preserve">A feel-good ad seeks confident, authentic plus-size women (30-80) and mature men for a mid-July shoot celebrating real people and healthy lifestyles. Talent will bring charisma to commercial scenes, follow direction for heartfelt moments, and potentially record ADR.
 </v>
       </c>
       <c r="E13" t="str">
-        <v>1 - 80</v>
+        <v>30 - 80</v>
       </c>
       <c r="F13" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G13" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673084/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674426/edit</v>
       </c>
       <c r="H13" t="str">
-        <v>06/09/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I13" t="str">
-        <v>United States</v>
+        <v>Sydney, Australia</v>
       </c>
       <c r="J13" t="str">
-        <v>https://www.exploretalent.com/auditions/1673084</v>
+        <v>https://www.exploretalent.com/auditions/1674426</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14">
-        <v>1673083</v>
+        <v>1673617</v>
       </c>
       <c r="B14" t="str">
-        <v>$7,500 Airlines Commercial Los Angeles Casting Call</v>
+        <v>Casting Call for Deodorant Social Media Films</v>
       </c>
       <c r="C14" t="str">
         <v>7500.00/ event</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">A national airline commercial seeks Caucasian women, 35-45, for a non-union shoot in LA. They need warm, relatable talent to portray modern passengers in an authentic campaign. Wardrobe fitting and potential overnight shooting required.
+        <v xml:space="preserve">A deodorant social media campaign seeks authentic, expressive individuals (18-80) comfortable sharing personal routines and creating content on camera. Digital-savvy personalities with interests like music, gaming, or cosplay are encouraged to apply for this one-day shoot. They are looking for raw, relatable talent, not traditional models.
 </v>
       </c>
       <c r="E14" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F14" t="str">
         <v>Any</v>
       </c>
       <c r="G14" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673083/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673617/edit</v>
       </c>
       <c r="H14" t="str">
-        <v>06/09/2025</v>
+        <v>07/07/2025</v>
       </c>
       <c r="I14" t="str">
-        <v>Los Angeles</v>
+        <v>United Kingdom</v>
       </c>
       <c r="J14" t="str">
-        <v>https://www.exploretalent.com/auditions/1673083</v>
+        <v>https://www.exploretalent.com/auditions/1673617</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15">
-        <v>1673082</v>
+        <v>1673818</v>
       </c>
       <c r="B15" t="str">
-        <v>Airlines Commercial Los Angeles Casting Call for Latin American Women</v>
+        <v>MODELS, ACTORS &amp; PERFORMERS FOR PATEK</v>
       </c>
       <c r="C15" t="str">
-        <v>7500.00/ event</v>
+        <v>7000.00/ event</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Airline commercial casting Latin American women (35-45) in Los Angeles. Seeking authentic, confident talent to portray everyday passengers. Local hires only, must be available for wardrobe fitting and possible overnight shoot.
+        <v xml:space="preserve">Luxury campaign casting models, actors, and performers (ages 16-70) with refined, expressive presence to showcase Patek Philippe timepieces. Seeking individuals embodying sophistication, precision, and artistry, with striking features and the ability to convey emotion subtly. Hand/wrist close-ups are essential.
 </v>
       </c>
       <c r="E15" t="str">
-        <v>1 - 80</v>
+        <v>16 - 70</v>
       </c>
       <c r="F15" t="str">
         <v>Any</v>
       </c>
       <c r="G15" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673082/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673818/edit</v>
       </c>
       <c r="H15" t="str">
-        <v>06/09/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I15" t="str">
-        <v>Los Angeles</v>
+        <v>N/A</v>
       </c>
       <c r="J15" t="str">
-        <v>https://www.exploretalent.com/auditions/1673082</v>
+        <v>https://www.exploretalent.com/auditions/1673818</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16">
-        <v>1673081</v>
+        <v>1674295</v>
       </c>
       <c r="B16" t="str">
-        <v>Airlines Commercial Los Angeles Casting Call</v>
+        <v>Casting Call for Fast Food Campaign</v>
       </c>
       <c r="C16" t="str">
-        <v>7500.00/ event</v>
+        <v>7000.00/ event</v>
       </c>
       <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">A national airline seeks Caucasian men, 55-65, for a well-paid, non-union commercial. Local talent with a relatable, warm presence and ability to take direction are needed to portray the everyday travel experience. Travel expenses are not covered.
+        <v xml:space="preserve">Fast food ad seeks authentic, energetic female or non-binary best friends (25-80) with vibrant personalities and unmatched chemistry. The shoot will capture natural friendship dynamics, genuine reactions, and enthusiasm. Professional collaboration is expected.
 </v>
       </c>
       <c r="E16" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F16" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G16" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673081/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674295/edit</v>
       </c>
       <c r="H16" t="str">
-        <v>06/09/2025</v>
+        <v>07/17/2025</v>
       </c>
       <c r="I16" t="str">
-        <v>Los Angeles</v>
+        <v>Sydney</v>
       </c>
       <c r="J16" t="str">
-        <v>https://www.exploretalent.com/auditions/1673081</v>
+        <v>https://www.exploretalent.com/auditions/1674295</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17">
-        <v>1673080</v>
+        <v>1673976</v>
       </c>
       <c r="B17" t="str">
-        <v>Airlines Commercial Los Angeles Casting Call for Real Families</v>
+        <v>Jewelry Campaign Casting Call for Barbers</v>
       </c>
       <c r="C17" t="str">
-        <v>7500.00/ event</v>
+        <v>6675.00/ event</v>
       </c>
       <c r="D17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Real families with two children (ages 5-10) are needed for an airline commercial. Seeking authentic family dynamics and natural on-camera chemistry. Families must be available for wardrobe fitting and potential overnight shoot, following direction while interacting naturally.
+        <v xml:space="preserve">A jewelry brand seeks a real, experienced male barber for a non-union commercial in Vancouver. The barber must be confident using clippers/shavers on camera to groom someone in a stylized setting. Availability for wardrobe fitting and shoot day is required.
 </v>
       </c>
       <c r="E17" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F17" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G17" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673080/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673976/edit</v>
       </c>
       <c r="H17" t="str">
-        <v>06/09/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="I17" t="str">
-        <v>Los Angeles</v>
+        <v>Vancouver</v>
       </c>
       <c r="J17" t="str">
-        <v>https://www.exploretalent.com/auditions/1673080</v>
+        <v>https://www.exploretalent.com/auditions/1673976</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18">
-        <v>1672524</v>
+        <v>1674349</v>
       </c>
       <c r="B18" t="str">
-        <v>Commercial Casting Call for Piano Players – National Campaign</v>
+        <v>Casting Call for Uber Marketing Campaign</v>
       </c>
       <c r="C18" t="str">
-        <v>7500.00/ event</v>
+        <v>6000.00/ event</v>
       </c>
       <c r="D18" t="str" xml:space="preserve">
-        <v xml:space="preserve">National commercial campaign seeks male piano players (35-50) with strong improv skills in jazz, classical, or contemporary styles. Filming in LA, the project features selected talent in three spots. Compensation includes fees, bonuses, and travel. All levels encouraged to apply.
+        <v xml:space="preserve">Uber seeks real, current rideshare/delivery drivers (no acting experience needed) in the U.S. or Canada for a marketing campaign.
 </v>
       </c>
       <c r="E18" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F18" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G18" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672524/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674349/edit</v>
       </c>
       <c r="H18" t="str">
-        <v>06/21/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="I18" t="str">
-        <v>N/A</v>
+        <v>Worldwide</v>
       </c>
       <c r="J18" t="str">
-        <v>https://www.exploretalent.com/auditions/1672524</v>
+        <v>https://www.exploretalent.com/auditions/1674349</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19">
-        <v>1672231</v>
+        <v>1674064</v>
       </c>
       <c r="B19" t="str">
-        <v>$6,000 Uber Commercial Casting Call for Riders and Drivers</v>
+        <v>Casting Call for Postal Services Commercial - Sydney</v>
       </c>
       <c r="C19" t="str">
         <v>6000.00/ event</v>
       </c>
       <c r="D19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Rideshare/delivery drivers can apply for paid marketing opportunities. Current/former drivers passionate about their experiences are encouraged to submit their information for consideration in digital ads and commercials. Selected drivers will be added to a casting database.
+        <v xml:space="preserve">Postal service campaign seeks vibrant, confident young adults (ages 20-80) for on-camera roles. The commercial celebrates youthful energy and diverse, relatable personalities. Talent must be comfortable in front of the camera and able to deliver dynamic, authentic performances in a professionally directed shoot.
 </v>
       </c>
       <c r="E19" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F19" t="str">
         <v>Any</v>
       </c>
       <c r="G19" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672231/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674064/edit</v>
       </c>
       <c r="H19" t="str">
-        <v>06/29/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="I19" t="str">
-        <v>N/A</v>
+        <v>Sydney</v>
       </c>
       <c r="J19" t="str">
-        <v>https://www.exploretalent.com/auditions/1672231</v>
+        <v>https://www.exploretalent.com/auditions/1674064</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20">
-        <v>1672045</v>
+        <v>1673289</v>
       </c>
       <c r="B20" t="str">
-        <v>Los Angeles - Beauty Line Campaign, $5500</v>
+        <v>Casting Call: Supermarket Commercial Campaign</v>
       </c>
       <c r="C20" t="str">
-        <v>5500.00/ n/a</v>
+        <v>6000.00/ event</v>
       </c>
       <c r="D20" t="str" xml:space="preserve">
-        <v xml:space="preserve">LA-based beauty line campaign seeks diverse talent (all genders, ethnicities, sizes) aged 13-70 with specific haircuts (bangs, layers, bob). Roles include millennial women/LGBTQ men, Gen X/Boomer women, Hispanic families, and Gen Z friends/sisters. Shoots June 17-19; hair prep June 16. Pays $250-$500 session, $1000-$5000 usage. Non-union.
+        <v xml:space="preserve">A major supermarket brand seeks real Australian families and individuals of all ages and backgrounds for an inclusive, authentic commercial. The campaign will capture genuine, everyday moments in a relaxed, family-friendly setting. Punctuality and responsiveness to direction are essential.
 </v>
       </c>
       <c r="E20" t="str">
-        <v>1 - 80</v>
+        <v>35 - 40</v>
       </c>
       <c r="F20" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G20" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672045/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673289/edit</v>
       </c>
       <c r="H20" t="str">
-        <v>06/05/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I20" t="str">
-        <v>Las Vegas, NV&gt;Los Angeles, CA&gt;San Diego, CA</v>
+        <v>Sydney, Australia</v>
       </c>
       <c r="J20" t="str">
-        <v>https://www.exploretalent.com/auditions/1672045</v>
+        <v>https://www.exploretalent.com/auditions/1673289</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21">
-        <v>1673106</v>
+        <v>1672231</v>
       </c>
       <c r="B21" t="str">
-        <v>America's Funniest People: Casting Funny Videos</v>
+        <v>$6,000 Uber Commercial Casting Call for Riders and Drivers</v>
       </c>
       <c r="C21" t="str">
-        <v>5000.00/ event</v>
+        <v>6000.00/ event</v>
       </c>
       <c r="D21" t="str" xml:space="preserve">
-        <v xml:space="preserve">"America's Funniest People" seeks video submissions of funny talents, skills, or comedic acts. Submit a video for a chance to be featured on TV and win $5,000 per episode. No live appearance is needed. Submit via the official casting form.
+        <v xml:space="preserve">Rideshare/delivery drivers (21-65) wanted for marketing campaigns. Share your experiences on camera in commercials and ads. Selected drivers join a casting database for potential national/regional exposure and professional branded production work. Must be available for scheduled shoots.
 </v>
       </c>
       <c r="E21" t="str">
-        <v>1 - 80</v>
+        <v>21 - 65</v>
       </c>
       <c r="F21" t="str">
         <v>Any</v>
       </c>
       <c r="G21" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673106/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672231/edit</v>
       </c>
       <c r="H21" t="str">
-        <v>07/03/2025</v>
+        <v>06/29/2025</v>
       </c>
       <c r="I21" t="str">
-        <v>Nationwide</v>
+        <v>N/A</v>
       </c>
       <c r="J21" t="str">
-        <v>https://www.exploretalent.com/auditions/1673106</v>
+        <v>https://www.exploretalent.com/auditions/1672231</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22">
-        <v>1672701</v>
+        <v>1674511</v>
       </c>
       <c r="B22" t="str">
-        <v>Antivirus Ad Commercial Casting Call for Host</v>
+        <v>Gymnasts Casting Call for Tech Commercial</v>
       </c>
       <c r="C22" t="str">
-        <v>4750.00/ event</v>
+        <v>5675.00/ event</v>
       </c>
       <c r="D22" t="str" xml:space="preserve">
-        <v xml:space="preserve">A cybersecurity brand seeks a confident, professional on-camera host for a web video campaign. The host will deliver scripted teleprompter reads with clarity, warmth, and authority, representing identity theft protection services. They must have a strong on-camera presence and maintain a business-appropriate look.
+        <v xml:space="preserve">Tech brand seeks energetic female gymnasts (20-35) for a Toronto commercial. Showcase floor routines with strong run-ups, flips, and landings. On-camera confidence and upbeat personality are key. Non-union, acting experience a plus. One-day shoot includes wardrobe fitting, meals, and insurance.
 </v>
       </c>
       <c r="E22" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F22" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G22" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672701/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674511/edit</v>
       </c>
       <c r="H22" t="str">
-        <v>06/20/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I22" t="str">
-        <v>New York City, New York</v>
+        <v>Canada</v>
       </c>
       <c r="J22" t="str">
-        <v>https://www.exploretalent.com/auditions/1672701</v>
+        <v>https://www.exploretalent.com/auditions/1674511</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
       <c r="A23">
-        <v>1672989</v>
+        <v>1674215</v>
       </c>
       <c r="B23" t="str">
-        <v>Casting Call – Outdoor Enthusiasts (Ages 20 to 50)</v>
+        <v>Casting for Major Liquor Brand Photoshoot</v>
       </c>
       <c r="C23" t="str">
-        <v>4600.00/ event</v>
+        <v>5550.00/ event</v>
       </c>
       <c r="D23" t="str" xml:space="preserve">
-        <v xml:space="preserve">Vancouver casting call for real outdoor enthusiasts (20-50) for a national commercial. No acting experience needed, just a love for hiking, running, or water sports. Be yourself and represent authentic outdoor lifestyles on screen.
+        <v xml:space="preserve">A major liquor brand is casting individuals aged 3-80 with distinctive and striking looks for an upcoming shoot. All ethnicities are welcome.
 </v>
       </c>
       <c r="E23" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F23" t="str">
         <v>Any</v>
       </c>
       <c r="G23" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672989/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674215/edit</v>
       </c>
       <c r="H23" t="str">
-        <v>06/28/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I23" t="str">
-        <v>Canada</v>
+        <v>Austin, TX, United States</v>
       </c>
       <c r="J23" t="str">
-        <v>https://www.exploretalent.com/auditions/1672989</v>
+        <v>https://www.exploretalent.com/auditions/1674215</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24">
-        <v>1672659</v>
+        <v>1673345</v>
       </c>
       <c r="B24" t="str">
-        <v>ULTA Commercial Casting Call</v>
+        <v>WellSpan Health Campaign Casting Call</v>
       </c>
       <c r="C24" t="str">
-        <v>4480.00/ event</v>
+        <v>5300.00/ event</v>
       </c>
       <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">A major beauty brand is casting confident models for its high-paying summer campaign. This is an opportunity to represent beauty, glamour, and elegance in a national photoshoot, enhancing portfolios with a premier client. Professionalism and poise are essential.
+        <v xml:space="preserve">Healthcare campaign seeks real people (18-80) in Pennsylvania to share their genuine healthcare experiences on camera. Participants will provide heartfelt testimonials about their personal journeys in on-camera interviews.
 </v>
       </c>
       <c r="E24" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F24" t="str">
         <v>Any</v>
       </c>
       <c r="G24" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672659/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673345/edit</v>
       </c>
       <c r="H24" t="str">
-        <v>06/19/2025</v>
+        <v>07/05/2025</v>
       </c>
       <c r="I24" t="str">
-        <v>United States</v>
+        <v>Pennsylvania</v>
       </c>
       <c r="J24" t="str">
-        <v>https://www.exploretalent.com/auditions/1672659</v>
+        <v>https://www.exploretalent.com/auditions/1673345</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
       <c r="A25">
-        <v>1673092</v>
+        <v>1674219</v>
       </c>
       <c r="B25" t="str">
-        <v>Pharmaceutical Campaign Atlanta Casting Call for Kids Ages 11-14</v>
+        <v>Nikon Korea Photo Shoot Casting</v>
       </c>
       <c r="C25" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ event</v>
       </c>
       <c r="D25" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking vibrant, diverse kids (11-14) for a non-union commercial campaign set in a middle school. Looking for authentic personalities, natural charm, and youthful energy. No prior experience needed. The shoot is documentary-style, emphasizing friendship, curiosity, and individuality.
+        <v xml:space="preserve">Houston photo shoot seeking male and female models (18-80, any ethnicity) for Nikon Korea publication in October 2025. Potential for ongoing work.
 </v>
       </c>
       <c r="E25" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F25" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G25" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673092/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674219/edit</v>
       </c>
       <c r="H25" t="str">
-        <v>06/09/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I25" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>United States</v>
       </c>
       <c r="J25" t="str">
-        <v>https://www.exploretalent.com/auditions/1673092</v>
+        <v>https://www.exploretalent.com/auditions/1674219</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26">
-        <v>1673091</v>
+        <v>1673610</v>
       </c>
       <c r="B26" t="str">
-        <v>Pharmaceutical Campaign Atlanta Casting Call: Latinx Kid Ages 11-14</v>
+        <v>Adidas Commercial Casting Call for Physical Therapist</v>
       </c>
       <c r="C26" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ event</v>
       </c>
       <c r="D26" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a charismatic Latinx boy (11-14) for a non-union, documentary-style commercial about middle school life. The spot aims for authenticity, warmth, and individuality, highlighting real friendships and genuine moments with a hopeful, lively tone.
+        <v xml:space="preserve">Adidas seeks a skilled female physical therapist (20-80) for a commercial. Ideal candidates are young professionals with authentic, reaction-based acting skills. Fittings and shoot occur mid-June.
 </v>
       </c>
       <c r="E26" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F26" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G26" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673091/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673610/edit</v>
       </c>
       <c r="H26" t="str">
-        <v>06/09/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I26" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Jacksonville</v>
       </c>
       <c r="J26" t="str">
-        <v>https://www.exploretalent.com/auditions/1673091</v>
+        <v>https://www.exploretalent.com/auditions/1673610</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27">
-        <v>1673090</v>
+        <v>1674478</v>
       </c>
       <c r="B27" t="str">
-        <v>Pharmaceutical Campaign Casting Call for Classroom History Costume Role</v>
+        <v>Alcohol Brand Commercial Sydney Casting Call</v>
       </c>
       <c r="C27" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ day</v>
       </c>
       <c r="D27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Non-union commercial seeks expressive 11-14 year olds to portray middle schoolers in historical costumes. The project aims for a cinematic, documentary feel, capturing authentic and spirited moments of school life. Ideal for creative, outgoing kids who love history and storytelling.
+        <v xml:space="preserve">Sydney casting call: Seeking a charismatic male actor (28-80) with a bold personality for a playful alcoholic ginger-beer commercial. Must deliver scripted dialogue with spontaneous energy, collaborating with the director for dynamic, refreshing shots.
 </v>
       </c>
       <c r="E27" t="str">
-        <v>1 - 80</v>
+        <v>28 - 80</v>
       </c>
       <c r="F27" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G27" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673090/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674478/edit</v>
       </c>
       <c r="H27" t="str">
-        <v>06/09/2025</v>
+        <v>07/19/2025</v>
       </c>
       <c r="I27" t="str">
-        <v>Atlanta, Georgia, United States</v>
+        <v>Australia</v>
       </c>
       <c r="J27" t="str">
-        <v>https://www.exploretalent.com/auditions/1673090</v>
+        <v>https://www.exploretalent.com/auditions/1674478</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28">
-        <v>1673089</v>
+        <v>1674117</v>
       </c>
       <c r="B28" t="str">
-        <v>Pharmaceutical Campaign Atlanta Casting Call for Teachers</v>
+        <v>Denim Campaign Model Casting in Los Angeles</v>
       </c>
       <c r="C28" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ event</v>
       </c>
       <c r="D28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a charismatic Black woman (30-40s) in Atlanta to play a confident, approachable, and authoritative middle school teacher for a non-union commercial. The project aims for a cinematic, documentary-style capturing heartwarming school moments.
+        <v xml:space="preserve">LA casting call for Black or ethnically ambiguous women, ages 24-30, with natural curves and a confident, rebellious vibe. Models should feel sexy and grounded while showcasing premium denim on June 24, embodying effortless poses and collaborating with the creative team.
 </v>
       </c>
       <c r="E28" t="str">
-        <v>1 - 80</v>
+        <v>24 - 80</v>
       </c>
       <c r="F28" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G28" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673089/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674117/edit</v>
       </c>
       <c r="H28" t="str">
-        <v>06/09/2025</v>
+        <v>07/14/2025</v>
       </c>
       <c r="I28" t="str">
-        <v>Atlanta, GA</v>
+        <v>California</v>
       </c>
       <c r="J28" t="str">
-        <v>https://www.exploretalent.com/auditions/1673089</v>
+        <v>https://www.exploretalent.com/auditions/1674117</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29">
-        <v>1673088</v>
+        <v>1673607</v>
       </c>
       <c r="B29" t="str">
-        <v>Pharmaceutical Campaign Atlanta Casting Call for Pep Rally Kids</v>
+        <v>Adidas Commercial Casting Call for Coach Physical Therapist</v>
       </c>
       <c r="C29" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ event</v>
       </c>
       <c r="D29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Non-union commercial seeks energetic 11-14 year olds for a documentary-style pep rally shoot. Portray spirited middle school students, showcasing school pride and enthusiasm in group scenes. A great opportunity to gain experience and build your resume.
+        <v xml:space="preserve">Commercial casting seeks a fit, authoritative male actor (40-80) with strong screen presence to play a coach/physical therapist. Must convey strength, composure, and deliver impactful reactions. Jacksonville filming; commercial/film experience preferred.
 </v>
       </c>
       <c r="E29" t="str">
-        <v>1 - 80</v>
+        <v>40 - 80</v>
       </c>
       <c r="F29" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G29" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673088/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673607/edit</v>
       </c>
       <c r="H29" t="str">
-        <v>06/09/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I29" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Jacksonville</v>
       </c>
       <c r="J29" t="str">
-        <v>https://www.exploretalent.com/auditions/1673088</v>
+        <v>https://www.exploretalent.com/auditions/1673607</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30">
-        <v>1673087</v>
+        <v>1673221</v>
       </c>
       <c r="B30" t="str">
-        <v>Pharmaceutical Campaign Casting Call for Gaga Ball Kids</v>
+        <v>Casting Cake Decorators for Netflix's "Is It Cake?"</v>
       </c>
       <c r="C30" t="str">
-        <v>4000.00/ event</v>
+        <v>5000.00/ event</v>
       </c>
       <c r="D30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking energetic 11-14 year olds for a non-union commercial featuring a Gaga Ball game. The production aims for a cinematic, documentary feel, capturing authentic middle school excitement. Real friends who love physical play and can bring genuine personality are encouraged to apply.
+        <v xml:space="preserve">Netflix's "Is It Cake?" seeks cake decorators for its 2025 season. Hosted by Mikey Day, contestants bake hyperrealistic cakes mimicking everyday objects to fool celebrity judges. Winners earn $5,000 per episode and a chance to win more by identifying real money from cake replicas.
 </v>
       </c>
       <c r="E30" t="str">
@@ -1376,2364 +1376,3717 @@
         <v>Any</v>
       </c>
       <c r="G30" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673087/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673221/edit</v>
       </c>
       <c r="H30" t="str">
-        <v>06/09/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I30" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Nationwide</v>
       </c>
       <c r="J30" t="str">
-        <v>https://www.exploretalent.com/auditions/1673087</v>
+        <v>https://www.exploretalent.com/auditions/1673221</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
       <c r="A31">
-        <v>1672790</v>
+        <v>1672989</v>
       </c>
       <c r="B31" t="str">
-        <v>Pharmaceutical Campaign Casting Call</v>
+        <v>Casting Call – Outdoor Enthusiasts (Ages 20 to 50)</v>
       </c>
       <c r="C31" t="str">
-        <v>4000.00/ event</v>
+        <v>4600.00/ event</v>
       </c>
       <c r="D31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pharmaceutical commercial casting real South Korean families, couples, and individuals for a heartwarming health and wellness campaign. Seeking authentic, multigenerational families for a relatable, lifestyle-driven shoot. No acting experience needed, just genuine connection. Fittings, Zoom interviews, and scheduled shoots required.
+        <v xml:space="preserve">Vancouver casting call for real outdoor enthusiasts (20-50) for a national commercial. No acting experience needed, just a passion for hiking, biking, fishing, or snow sports. Must be comfortable navigating outdoor terrain and following direction. All genders and ethnicities welcome.
 </v>
       </c>
       <c r="E31" t="str">
-        <v>1 - 80</v>
+        <v>20 - 50</v>
       </c>
       <c r="F31" t="str">
         <v>Any</v>
       </c>
       <c r="G31" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672790/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672989/edit</v>
       </c>
       <c r="H31" t="str">
-        <v>06/16/2025</v>
+        <v>06/28/2025</v>
       </c>
       <c r="I31" t="str">
         <v>Canada</v>
       </c>
       <c r="J31" t="str">
-        <v>https://www.exploretalent.com/auditions/1672790</v>
+        <v>https://www.exploretalent.com/auditions/1672989</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
       <c r="A32">
-        <v>1672315</v>
+        <v>1674532</v>
       </c>
       <c r="B32" t="str">
-        <v>Remitly Commercial Casting Call for Vietnamese Male Actor</v>
+        <v>Casting for Wrangler Jeans TV Commercial</v>
       </c>
       <c r="C32" t="str">
-        <v>3750.00/ event</v>
+        <v>4000.00/ event</v>
       </c>
       <c r="D32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nationwide commercial seeks a charismatic, energetic Vietnamese male actor (30-50) to portray a passionate sports fan. Must be likable, comfortable on camera, and possess comedic flair. Travel to New York, fitting required, competitive pay. Improv skills a plus.
+        <v xml:space="preserve">Wrangler Jeans is casting authentic and stylish individuals, aged 18-80, for an upcoming TV and print campaign. All ethnicities are welcome to represent the brand's image.
 </v>
       </c>
       <c r="E32" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F32" t="str">
         <v>Any</v>
       </c>
       <c r="G32" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672315/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674532/edit</v>
       </c>
       <c r="H32" t="str">
-        <v>06/27/2025</v>
+        <v>07/05/2025</v>
       </c>
       <c r="I32" t="str">
-        <v>N/A</v>
+        <v>Calgary, AB, Canada</v>
       </c>
       <c r="J32" t="str">
-        <v>https://www.exploretalent.com/auditions/1672315</v>
+        <v>https://www.exploretalent.com/auditions/1674532</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
       <c r="A33">
-        <v>1672830</v>
+        <v>1674576</v>
       </c>
       <c r="B33" t="str">
-        <v>$3,750+ Medical Product Commercial Casting Call</v>
+        <v>Road Trip Commercial Casting Call for Friend Groups</v>
       </c>
       <c r="C33" t="str">
-        <v>3750.00/ event</v>
+        <v>4000.00/ event</v>
       </c>
       <c r="D33" t="str" xml:space="preserve">
-        <v xml:space="preserve">A medical product commercial seeks authentic, working-class individuals with Post-COPD experience to portray resilience. The campaign aims to tell a human-centered story through honest, emotionally grounded performances.
+        <v xml:space="preserve">A commercial seeks three adventurous friends in their twenties for a paid road trip. The production will document their genuine interactions and laughter. No acting experience is needed, just authentic friendship, energy, and a cooperative attitude to capture key story beats. On-screen credit and footage provided.
 </v>
       </c>
       <c r="E33" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F33" t="str">
         <v>Any</v>
       </c>
       <c r="G33" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672830/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674576/edit</v>
       </c>
       <c r="H33" t="str">
-        <v>06/15/2025</v>
+        <v>07/23/2025</v>
       </c>
       <c r="I33" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Connecticut, United States</v>
       </c>
       <c r="J33" t="str">
-        <v>https://www.exploretalent.com/auditions/1672830</v>
+        <v>https://www.exploretalent.com/auditions/1674576</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
       <c r="A34">
-        <v>1672525</v>
+        <v>1673879</v>
       </c>
       <c r="B34" t="str">
-        <v>Medical Product Commercial Casting Call for Real People in Atlanta</v>
+        <v>Casting Call for Therapists: Webinar Project</v>
       </c>
       <c r="C34" t="str">
-        <v>3675.00/ event</v>
+        <v>4000.00/ event</v>
       </c>
       <c r="D34" t="str" xml:space="preserve">
-        <v xml:space="preserve">A national TV show seeks families and communities nationwide with extraordinary Christmas light displays to compete for a $50,000 prize. Participants should showcase massive light displays, intricate designs, synchronized music, animation, and overall creativity. Passionate decorators ready to share their holiday magic are encouraged to apply.
+        <v xml:space="preserve">Licensed therapists and social workers are needed for a webinar-style video. Share your expertise and patient care strategies in an authentic, recorded conversation. No media experience required. The project aims to represent the field with sincerity and professionalism.
 </v>
       </c>
       <c r="E34" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F34" t="str">
         <v>Any</v>
       </c>
       <c r="G34" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672525/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673879/edit</v>
       </c>
       <c r="H34" t="str">
-        <v>06/21/2025</v>
+        <v>07/10/2025</v>
       </c>
       <c r="I34" t="str">
-        <v>Atlanta, Georgia, United States</v>
+        <v>Chicago, Illinois, United States</v>
       </c>
       <c r="J34" t="str">
-        <v>https://www.exploretalent.com/auditions/1672525</v>
+        <v>https://www.exploretalent.com/auditions/1673879</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
       <c r="A35">
-        <v>1673005</v>
+        <v>1673706</v>
       </c>
       <c r="B35" t="str">
-        <v>Energetic Gamer Role in Comedy Drama Series Casting</v>
+        <v>Casting Call for Paris Sportswear Campaign</v>
       </c>
       <c r="C35" t="str">
-        <v>3600.00/ event</v>
+        <v>4000.00/ event</v>
       </c>
       <c r="D35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Comedy-drama seeks "Chase," a playful, driven gamer with a bold personality, for a series about influencers in digital rehab rebuilding their careers. Chase brings humor and competition to the group. Paid opportunity with IMDb credit.
+        <v xml:space="preserve">Sportswear brand seeks unsigned models, athletes, talents, and micro-influencers (ages 3-80) with authenticity, energy, and style for a global campaign. This is a chance to break into the industry through a professional photoshoot, representing a modern, athletic, and inclusive aesthetic.
 </v>
       </c>
       <c r="E35" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F35" t="str">
         <v>Any</v>
       </c>
       <c r="G35" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673005/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673706/edit</v>
       </c>
       <c r="H35" t="str">
-        <v>06/12/2025</v>
+        <v>07/09/2025</v>
       </c>
       <c r="I35" t="str">
-        <v>United States</v>
+        <v>France</v>
       </c>
       <c r="J35" t="str">
-        <v>https://www.exploretalent.com/auditions/1673005</v>
+        <v>https://www.exploretalent.com/auditions/1673706</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36">
-        <v>1673004</v>
+        <v>1673333</v>
       </c>
       <c r="B36" t="str">
-        <v>Charismatic Male Role in Comedy Drama Series Casting</v>
+        <v>Adidas Commercial Casting: Grandma Role</v>
       </c>
       <c r="C36" t="str">
-        <v>3600.00/ event</v>
+        <v>3650.00/ event</v>
       </c>
       <c r="D36" t="str" xml:space="preserve">
-        <v xml:space="preserve">"Alex" is a flashy, confident influencer in a new comedy-drama about former social media stars rebuilding their brands at a training school. The role offers comic relief, sharp charisma, paid work, and IMDb credit.
+        <v xml:space="preserve">Seeking a charming, expressive older woman (70-80) for a "diner grandma" role in a retro commercial. Must portray a sweet, spirited, and slightly sassy grandmotherly figure with warmth, humor, and authenticity, following direction while staying in character.
 </v>
       </c>
       <c r="E36" t="str">
-        <v>1 - 80</v>
+        <v>70 - 80</v>
       </c>
       <c r="F36" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G36" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673004/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673333/edit</v>
       </c>
       <c r="H36" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I36" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J36" t="str">
-        <v>https://www.exploretalent.com/auditions/1673004</v>
+        <v>https://www.exploretalent.com/auditions/1673333</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37">
-        <v>1673002</v>
+        <v>1673660</v>
       </c>
       <c r="B37" t="str">
-        <v>Influencer Coach Role in Comedy Drama Series Casting</v>
+        <v>Adidas Commercial Casting for Baseball Scout</v>
       </c>
       <c r="C37" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Comedy-drama series seeks a passionate actor to play an Influencer Coach at a training school. Paid opportunity with IMDb credit. Expect humor, personal growth, and satire in the digital age.
+        <v xml:space="preserve">Seeking a seasoned male actor (50-80) to portray a classic, skeptical baseball scout for a nostalgic commercial. Must embody wisdom, authenticity, and a sharp eye for talent, delivering grounded realism and collaborating with directors to add nuance.
 </v>
       </c>
       <c r="E37" t="str">
-        <v>1 - 80</v>
+        <v>50 - 80</v>
       </c>
       <c r="F37" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G37" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673002/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673660/edit</v>
       </c>
       <c r="H37" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I37" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J37" t="str">
-        <v>https://www.exploretalent.com/auditions/1673002</v>
+        <v>https://www.exploretalent.com/auditions/1673660</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38">
-        <v>1673001</v>
+        <v>1673340</v>
       </c>
       <c r="B38" t="str">
-        <v>Father Figure Role in Comedy Drama Casting Call</v>
+        <v>Adidas Commercial Casting: Senior Diner Waitress</v>
       </c>
       <c r="C38" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D38" t="str" xml:space="preserve">
-        <v xml:space="preserve">Carmen Cuba Casting seeks an actor for Mr. Cooper in a comedy-drama about ex-influencers in digital rehab. Mr. Cooper, father to a lead, embodies generational conflict and ambition. Paid role with IMDb credit.
+        <v xml:space="preserve">Seeking a seasoned actress (50-80) for a nostalgic commercial. Must embody a warm, no-nonsense senior diner waitress with authority and authenticity. Strong presence, natural delivery, and ability to take direction are essential. Fitting required.
 </v>
       </c>
       <c r="E38" t="str">
-        <v>1 - 80</v>
+        <v>50 - 80</v>
       </c>
       <c r="F38" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G38" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673001/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673340/edit</v>
       </c>
       <c r="H38" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I38" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J38" t="str">
-        <v>https://www.exploretalent.com/auditions/1673001</v>
+        <v>https://www.exploretalent.com/auditions/1673340</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
       <c r="A39">
-        <v>1673000</v>
+        <v>1673339</v>
       </c>
       <c r="B39" t="str">
-        <v>Confident Female Role in Comedy Drama Series Casting</v>
+        <v>Adidas Commercial Casting Call for Diner Cook</v>
       </c>
       <c r="C39" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D39" t="str" xml:space="preserve">
-        <v xml:space="preserve">Casting Demi, a smart, confident, and humorous standout in a comedy-drama about former social media stars at an influencer training school. This paid, non-union role requires wit, relatability, and emotional intelligence to balance the ensemble cast as they navigate digital burnout and reinvention. IMDb credit included.
+        <v xml:space="preserve">Adidas commercial casting a male actor (35-80) for a Diner Cook role. Must embody the gritty, fast-paced diner environment with confident body language, believable kitchen skills, and strong character consistency while interacting with other cast members.
 </v>
       </c>
       <c r="E39" t="str">
-        <v>1 - 80</v>
+        <v>35 - 80</v>
       </c>
       <c r="F39" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G39" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673000/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673339/edit</v>
       </c>
       <c r="H39" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I39" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J39" t="str">
-        <v>https://www.exploretalent.com/auditions/1673000</v>
+        <v>https://www.exploretalent.com/auditions/1673339</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40">
-        <v>1672999</v>
+        <v>1673338</v>
       </c>
       <c r="B40" t="str">
-        <v>Female Role in Influencer Comedy Drama Casting</v>
+        <v>Adidas Commercial Casting Call for Diner Patrons</v>
       </c>
       <c r="C40" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D40" t="str" xml:space="preserve">
-        <v xml:space="preserve">A comedy-drama seeks talent for Lila, a sharp, sarcastic influencer at a "reboot" school. This non-union, paid role (IMDb credit) requires comedic timing and a bold, bossy attitude. Contribute to an ensemble cast exploring influencer culture's highs and lows. Filming mid-June 2025.
+        <v xml:space="preserve">Adidas seeks two male actors (50-80) for a diner commercial. They should embody opinionated, East Coast "old heads" with strong screen presence, humor, and authentic chemistry. Actors must confidently deliver lines and take direction while adding personal flair.
 </v>
       </c>
       <c r="E40" t="str">
-        <v>1 - 80</v>
+        <v>50 - 80</v>
       </c>
       <c r="F40" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G40" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672999/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673338/edit</v>
       </c>
       <c r="H40" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I40" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J40" t="str">
-        <v>https://www.exploretalent.com/auditions/1672999</v>
+        <v>https://www.exploretalent.com/auditions/1673338</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41">
-        <v>1672998</v>
+        <v>1673336</v>
       </c>
       <c r="B41" t="str">
-        <v>Food Review Content Creator Role Casting Call</v>
+        <v>Adidas Commercial Casting for NBA Baby Version</v>
       </c>
       <c r="C41" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">A humorous series seeks actors for social media stars facing fading fame at a digital detox school. This non-union, paid opportunity offers IMDb credit. Seeking a mature, introspective influencer and a quiet, strong food reviewer to collaborate on authentic, emotionally grounded scenes.
+        <v xml:space="preserve">Seeking an adorable, calm, and expressive African American toddler to portray a baby NBA player in a commercial. Must be comfortable on set, cooperative, and have natural screen presence. Parents must accompany the child.
 </v>
       </c>
       <c r="E41" t="str">
-        <v>1 - 80</v>
+        <v>2 - 80</v>
       </c>
       <c r="F41" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G41" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672998/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673336/edit</v>
       </c>
       <c r="H41" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I41" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J41" t="str">
-        <v>https://www.exploretalent.com/auditions/1672998</v>
+        <v>https://www.exploretalent.com/auditions/1673336</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42">
-        <v>1672997</v>
+        <v>1673335</v>
       </c>
       <c r="B42" t="str">
-        <v>Fitness Content Creator Role in Comedy-Drama Series Casting</v>
+        <v>Adidas Commercial Casting for Tall Male Actor</v>
       </c>
       <c r="C42" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D42" t="str" xml:space="preserve">
-        <v xml:space="preserve">A new series follows former social media stars in a training school as they navigate personal growth, competition, and their online identities to regain relevance. This paid, non-union opportunity offers IMDb credit and is ideal for actors building their resumes.
+        <v xml:space="preserve">Seeking a tall, striking male actor (20-80) for a visually impactful commercial role. Must exude confidence, charisma, and command presence with physicality. Needs to deliver subtle, expressive performance, interact naturally, and be comfortable on camera. Fitting required.
 </v>
       </c>
       <c r="E42" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F42" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G42" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672997/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673335/edit</v>
       </c>
       <c r="H42" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I42" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J42" t="str">
-        <v>https://www.exploretalent.com/auditions/1672997</v>
+        <v>https://www.exploretalent.com/auditions/1673335</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43">
-        <v>1672996</v>
+        <v>1673334</v>
       </c>
       <c r="B43" t="str">
-        <v>Fashion Content Creator Casting</v>
+        <v>Adidas Commercial Casting for New Yorker Girl</v>
       </c>
       <c r="C43" t="str">
         <v>3600.00/ event</v>
       </c>
       <c r="D43" t="str" xml:space="preserve">
-        <v xml:space="preserve">A comedy-drama seeks actors for a key role about washed-up influencers attending a training school to revive their careers. They'll face personal struggles and comedic situations. Paid, non-union, and includes IMDb credit.
+        <v xml:space="preserve">Adidas seeks a confident, stylish young woman to play a bold, opinionated, and authentic New Yorker. She must have a commanding presence, deliver lines with sass and humor, take direction, and embody the vibrant energy of city life.
 </v>
       </c>
       <c r="E43" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F43" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G43" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672996/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673334/edit</v>
       </c>
       <c r="H43" t="str">
-        <v>06/12/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I43" t="str">
-        <v>United States</v>
+        <v>Miami</v>
       </c>
       <c r="J43" t="str">
-        <v>https://www.exploretalent.com/auditions/1672996</v>
+        <v>https://www.exploretalent.com/auditions/1673334</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44">
-        <v>1672401</v>
+        <v>1673331</v>
       </c>
       <c r="B44" t="str">
-        <v>Major Cat Food Brand Commercial Casting Call for Cat Lovers</v>
+        <v>Adidas Commercial Casting Call for Audience Member</v>
       </c>
       <c r="C44" t="str">
-        <v>3550.00/ event</v>
+        <v>3600.00/ event</v>
       </c>
       <c r="D44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Cat food brand seeks Austin-based, photogenic cat lovers (ages 20-45) for a paid print campaign. Must be comfortable handling cats and available for callbacks the week of June 2. The shoot aims to capture authentic moments reflecting the modern cat owner lifestyle. National brand exposure included.
+        <v xml:space="preserve">Commercial seeks a tall, athletic male actor (20-80 years old, 6'4"+) to convincingly portray a basketball player in the audience. Must blend in, possess strong on-camera presence, deliver emotionally expressive reactions (including sadness), and follow direction to enhance the sports atmosphere.
 </v>
       </c>
       <c r="E44" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F44" t="str">
         <v>Any</v>
       </c>
       <c r="G44" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672401/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673331/edit</v>
       </c>
       <c r="H44" t="str">
-        <v>06/26/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I44" t="str">
-        <v>Austin, Texas</v>
+        <v>Miami</v>
       </c>
       <c r="J44" t="str">
-        <v>https://www.exploretalent.com/auditions/1672401</v>
+        <v>https://www.exploretalent.com/auditions/1673331</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45">
-        <v>1672819</v>
+        <v>1673329</v>
       </c>
       <c r="B45" t="str">
-        <v>Cable Company Ad Nationwide Casting Call for Skaters</v>
+        <v>Adidas Commercial Casting for Milkshake Kid</v>
       </c>
       <c r="C45" t="str">
-        <v>3500.00/ event</v>
+        <v>3600.00/ event</v>
       </c>
       <c r="D45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Major cable company seeks expert female figure and speed skaters nationwide for a paid commercial shoot in Los Angeles. All travel expenses covered. Showcase your skills in a national ad!
+        <v xml:space="preserve">Seeking a charismatic girl (5-8) for a heartwarming commercial. She'll portray a playful, expressive kid enjoying a milkshake at a diner, radiating charm, sass, and a disarming smile while following direction and bringing a joyful, nostalgic moment to life.
 </v>
       </c>
       <c r="E45" t="str">
-        <v>1 - 80</v>
+        <v>5 - 80</v>
       </c>
       <c r="F45" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G45" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672819/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673329/edit</v>
       </c>
       <c r="H45" t="str">
-        <v>06/15/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I45" t="str">
-        <v>N/A</v>
+        <v>Miami</v>
       </c>
       <c r="J45" t="str">
-        <v>https://www.exploretalent.com/auditions/1672819</v>
+        <v>https://www.exploretalent.com/auditions/1673329</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46">
-        <v>1672668</v>
+        <v>1674536</v>
       </c>
       <c r="B46" t="str">
-        <v>Dentist Needed for Commercial</v>
+        <v>Marc Jacobs Commercial Casting</v>
       </c>
       <c r="C46" t="str">
         <v>3500.00/ event</v>
       </c>
       <c r="D46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Colgate seeks UK dentists for an upcoming commercial. No acting experience needed, just authenticity and confidence. Represent your profession in a national campaign, filming in Georgia for several days in a still or video shoot.
+        <v xml:space="preserve">Marc Jacobs seeks diverse individuals (all ethnicities, ages, abilities, skin types) for a commercial photo/video shoot. No experience needed; unique style and personality are key.
 </v>
       </c>
       <c r="E46" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F46" t="str">
         <v>Any</v>
       </c>
       <c r="G46" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672668/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674536/edit</v>
       </c>
       <c r="H46" t="str">
-        <v>06/19/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I46" t="str">
-        <v>United Kingdom</v>
+        <v>New York, NY, United States</v>
       </c>
       <c r="J46" t="str">
-        <v>https://www.exploretalent.com/auditions/1672668</v>
+        <v>https://www.exploretalent.com/auditions/1674536</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47">
-        <v>1672284</v>
+        <v>1674402</v>
       </c>
       <c r="B47" t="str">
-        <v>JC Penny Commercial Casting Call for National Retail Campaign</v>
+        <v>Casting Call for Boutique Hotel Commercial</v>
       </c>
       <c r="C47" t="str">
-        <v>3150.00/ event</v>
+        <v>3500.00/ event</v>
       </c>
       <c r="D47" t="str" xml:space="preserve">
-        <v xml:space="preserve">A major retail brand seeks dynamic, relatable talent (ages 20-45, all ethnicities) with strong on-camera presence for a commercial campaign. Selected individuals will represent the brand professionally, follow direction, and exhibit punctuality on set. Availability on the shoot date is essential.
+        <v xml:space="preserve">Real romantic partners (28-80) needed for a stylish boutique hotel commercial. Showcase genuine chemistry in natural couple moments, guided by the director. Collaborate to maintain a cohesive visual narrative. Camera tests and a full-day shoot required.
 </v>
       </c>
       <c r="E47" t="str">
-        <v>1 - 80</v>
+        <v>28 - 80</v>
       </c>
       <c r="F47" t="str">
         <v>Any</v>
       </c>
       <c r="G47" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672284/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674402/edit</v>
       </c>
       <c r="H47" t="str">
-        <v>06/28/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="I47" t="str">
-        <v>N/A</v>
+        <v>Charleston, South Carolina</v>
       </c>
       <c r="J47" t="str">
-        <v>https://www.exploretalent.com/auditions/1672284</v>
+        <v>https://www.exploretalent.com/auditions/1674402</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48">
-        <v>1672295</v>
+        <v>1674425</v>
       </c>
       <c r="B48" t="str">
-        <v>Cruise Ship Casting Call for Dancers with Singing or Aerial Skills</v>
+        <v>Ride Service Campaign Casting - Sydney</v>
       </c>
       <c r="C48" t="str">
-        <v>3050.00/ month</v>
+        <v>3500.00/ event</v>
       </c>
       <c r="D48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Luxury cruise line seeks talented dancers (male/female) with strong singing or aerial skills for onboard performances. Rehearsals in Germany, contract through fall. Professional dance experience required; stage/cruise experience a plus. Must be available for full contract.
+        <v xml:space="preserve">Ride-share campaign casting diverse Australian talent (all ethnicities, ages 18-80) for cinematic vignettes in early July. Seeking character-driven riders and drivers who can deliver natural performances, take direction well, and collaborate professionally. Credit and footage provided.
 </v>
       </c>
       <c r="E48" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F48" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G48" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672295/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674425/edit</v>
       </c>
       <c r="H48" t="str">
-        <v>06/27/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I48" t="str">
-        <v>N/A</v>
+        <v>Sydney, Australia</v>
       </c>
       <c r="J48" t="str">
-        <v>https://www.exploretalent.com/auditions/1672295</v>
+        <v>https://www.exploretalent.com/auditions/1674425</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
       <c r="A49">
-        <v>1672625</v>
+        <v>1674403</v>
       </c>
       <c r="B49" t="str">
-        <v>$3,000 Cinemark Gamescape Commercial Casting</v>
+        <v>Aged Care Campaign Casting in Sydney</v>
       </c>
       <c r="C49" t="str">
-        <v>3000.00/ event</v>
+        <v>3500.00/ event</v>
       </c>
       <c r="D49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking energetic individuals for a paid commercial shoot in El Paso, TX (week of June 9) showcasing entertainment and adventure. Ideal candidates enjoy teamwork, activities like bowling and climbing, and have a playful personality. Great visibility opportunity!
+        <v xml:space="preserve">Aged care campaign casting seeks a real older couple (60-80s, male) to portray authentic warmth and connection. The project is a professional advertising shoot.
 </v>
       </c>
       <c r="E49" t="str">
-        <v>1 - 80</v>
+        <v>60 - 80</v>
       </c>
       <c r="F49" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G49" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672625/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674403/edit</v>
       </c>
       <c r="H49" t="str">
-        <v>06/20/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="I49" t="str">
-        <v>El Paso, Texas</v>
+        <v>Sydney, Australia</v>
       </c>
       <c r="J49" t="str">
-        <v>https://www.exploretalent.com/auditions/1672625</v>
+        <v>https://www.exploretalent.com/auditions/1674403</v>
       </c>
     </row>
     <row r="50" xml:space="preserve">
       <c r="A50">
-        <v>1672789</v>
+        <v>1674345</v>
       </c>
       <c r="B50" t="str">
-        <v>Casting Call: Pet Healthcare Campaign - Sydney</v>
+        <v>Financial Stills Ad Casting Call</v>
       </c>
       <c r="C50" t="str">
-        <v>2500.00/ event</v>
+        <v>3450.00/ event</v>
       </c>
       <c r="D50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Sydney campaign seeks dog lovers of all ages to showcase their bond with pets in a heartwarming commercial promoting animal care. On-camera opportunity to interact with dogs and convey an authentic connection.
+        <v xml:space="preserve">A financial stills campaign seeks real tradespersons (18-80) in Ontario. No on-set experience needed. Submit name, age, occupation, location, contact info, and recent photos (ideally work-related).
 </v>
       </c>
       <c r="E50" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F50" t="str">
         <v>Any</v>
       </c>
       <c r="G50" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672789/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674345/edit</v>
       </c>
       <c r="H50" t="str">
-        <v>06/16/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="I50" t="str">
-        <v>Sydney, Australia</v>
+        <v>Toronto, ON, Canada</v>
       </c>
       <c r="J50" t="str">
-        <v>https://www.exploretalent.com/auditions/1672789</v>
+        <v>https://www.exploretalent.com/auditions/1674345</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51">
-        <v>1673182</v>
+        <v>1672284</v>
       </c>
       <c r="B51" t="str">
-        <v>Adidas Commercial Casting Call</v>
+        <v>JC Penny Commercial Casting Call for National Retail Campaign</v>
       </c>
       <c r="C51" t="str">
-        <v>2250.00/ event</v>
+        <v>3150.00/ event</v>
       </c>
       <c r="D51" t="str" xml:space="preserve">
-        <v xml:space="preserve">A commercial production seeks diverse male/female actors and models (20-45) for a well-paid, one-day shoot. Talent will portray authentic characters in scripted or lifestyle scenes, following direction from the production team. Professionalism and preparation are essential.
+        <v xml:space="preserve">JCPenney commercial casting a dynamic female lead, aged 20-45, any ethnicity. Seeking a talent with a strong on-camera presence to represent the brand positively.
 </v>
       </c>
       <c r="E51" t="str">
-        <v>1 - 80</v>
+        <v>20 - 45</v>
       </c>
       <c r="F51" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G51" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673182/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672284/edit</v>
       </c>
       <c r="H51" t="str">
-        <v>07/04/2025</v>
+        <v>06/28/2025</v>
       </c>
       <c r="I51" t="str">
-        <v>United States</v>
+        <v>N/A</v>
       </c>
       <c r="J51" t="str">
-        <v>https://www.exploretalent.com/auditions/1673182</v>
+        <v>https://www.exploretalent.com/auditions/1672284</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
       <c r="A52">
-        <v>1672342</v>
+        <v>1674171</v>
       </c>
       <c r="B52" t="str">
-        <v>New Orleans Casting Call for Female Law Enforcement or Military Talent</v>
+        <v>Basketball Players for Athletic Gear Campaign</v>
       </c>
       <c r="C52" t="str">
-        <v>2000.00/ day</v>
+        <v>3000.00/ event</v>
       </c>
       <c r="D52" t="str" xml:space="preserve">
-        <v xml:space="preserve">High-profile production seeks a non-union female, ages 30-50, with law enforcement or military experience for a well-paid, one-day featured role. The role requires a commanding presence and authentic authority.
+        <v xml:space="preserve">Athletic brand casting call: Male and female basketball players, ages 3-80, of all ethnicities are needed for a photo and video shoot. Availability for fitting, rehearsal, and the shoot day is required.
 </v>
       </c>
       <c r="E52" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F52" t="str">
         <v>Any</v>
       </c>
       <c r="G52" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672342/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674171/edit</v>
       </c>
       <c r="H52" t="str">
-        <v>06/30/2025</v>
+        <v>07/15/2025</v>
       </c>
       <c r="I52" t="str">
-        <v>New Orleans, Louisiana</v>
+        <v>Miami, FL</v>
       </c>
       <c r="J52" t="str">
-        <v>https://www.exploretalent.com/auditions/1672342</v>
+        <v>https://www.exploretalent.com/auditions/1674171</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53">
-        <v>1672324</v>
+        <v>1674882</v>
       </c>
       <c r="B53" t="str">
-        <v>International Mobile Phone Commercial Casting Call for Male Podcast Host Jordan</v>
+        <v>Casting Female Hikers for Outdoorwear Campaign</v>
       </c>
       <c r="C53" t="str">
-        <v>2000.00/ negotiable</v>
+        <v>3000.00/ event</v>
       </c>
       <c r="D53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a male (20-30) podcast host "Jordan" for an international mobile phone commercial filming in Thailand. Must have excellent English, a strong on-camera presence, and a thoughtful personality. Valid passport and availability for international travel are required. All ethnicities are welcome.
+        <v xml:space="preserve">Outdoor apparel brand seeks adventurous women (23-80) with diverse backgrounds for a hiking campaign. Real hikers confident in natural settings will showcase activewear, embodying strength and resilience while following creative direction.
 </v>
       </c>
       <c r="E53" t="str">
-        <v>1 - 80</v>
+        <v>23 - 80</v>
       </c>
       <c r="F53" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G53" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672324/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674882/edit</v>
       </c>
       <c r="H53" t="str">
-        <v>06/27/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I53" t="str">
-        <v>N/A</v>
+        <v>Germany</v>
       </c>
       <c r="J53" t="str">
-        <v>https://www.exploretalent.com/auditions/1672324</v>
+        <v>https://www.exploretalent.com/auditions/1674882</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
       <c r="A54">
-        <v>1672070</v>
+        <v>1673308</v>
       </c>
       <c r="B54" t="str">
-        <v>Nationwide - Celsius Voiceover, $2000</v>
+        <v>Commercial Casting Call for Hero Girl</v>
       </c>
       <c r="C54" t="str">
-        <v>2000.00/ n/a</v>
+        <v>3000.00/ event</v>
       </c>
       <c r="D54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Nationwide Celsius voiceover casting call: $500 session, $1500 buyout (-20%AF). Seeking English and Spanish speakers (bilingual preferred). Source Connect not required; record with preferred program or studio (at your expense). Also casting Christmas light decorators for a show with a $50,000 prize.
+        <v xml:space="preserve">A major commercial campaign seeks a dynamic woman (age 3-80, any ethnicity) for a one-day "Hero Girl" shoot. This is a lead role, offering significant exposure for a model/actor who can deliver a powerful and engaging on-camera presence.
 </v>
       </c>
       <c r="E54" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F54" t="str">
         <v>Any</v>
       </c>
       <c r="G54" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672070/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673308/edit</v>
       </c>
       <c r="H54" t="str">
-        <v>06/06/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I54" t="str">
-        <v>N/A</v>
+        <v>Sydney, Australia</v>
       </c>
       <c r="J54" t="str">
-        <v>https://www.exploretalent.com/auditions/1672070</v>
+        <v>https://www.exploretalent.com/auditions/1673308</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
       <c r="A55">
-        <v>1673133</v>
+        <v>1674732</v>
       </c>
       <c r="B55" t="str">
-        <v>Dove Campaign Casting Call: Teen Athletes</v>
+        <v>Disney Commercial Casting Call</v>
       </c>
       <c r="C55" t="str">
-        <v>2000.00/ event</v>
+        <v>2500.00/ event</v>
       </c>
       <c r="D55" t="str" xml:space="preserve">
-        <v xml:space="preserve">A national campaign seeks authentic teen female athletes in competitive team sports to be the face of youth sports, celebrating strength and diversity. Individual and team submissions are encouraged.
+        <v xml:space="preserve">Major studio production seeks diverse male and female talent (ages 20-80, all ethnicities) for various roles. Performers should be professional, adaptable, and collaborative, ready to take direction and deliver authentic performances on set.
 </v>
       </c>
       <c r="E55" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F55" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G55" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673133/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674732/edit</v>
       </c>
       <c r="H55" t="str">
-        <v>07/03/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I55" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J55" t="str">
-        <v>https://www.exploretalent.com/auditions/1673133</v>
+        <v>https://www.exploretalent.com/auditions/1674732</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
       <c r="A56">
-        <v>1672970</v>
+        <v>1674531</v>
       </c>
       <c r="B56" t="str">
-        <v>Insurance Advert Commercial Casting Call</v>
+        <v>Casting for Victoria's Secret &amp; PINK Commercial</v>
       </c>
       <c r="C56" t="str">
-        <v>2000.00/ event</v>
+        <v>2500.00/ event</v>
       </c>
       <c r="D56" t="str" xml:space="preserve">
-        <v xml:space="preserve">London-based, real couples wanted for an insurance commercial. Non-actors who naturally convey connection will be filmed in a lifestyle setting. The shoot includes a paid mini-break in France for unscripted interactions used online and on social media. Simple filming schedule over several days.
+        <v xml:space="preserve">Victoria's Secret &amp; PINK seeks confident, dynamic women (18-80, any ethnicity) for a commercial. Selected talent will gain exposure on their social media, website, and app, participating in a high-profile campaign.
 </v>
       </c>
       <c r="E56" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F56" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G56" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672970/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674531/edit</v>
       </c>
       <c r="H56" t="str">
-        <v>07/02/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I56" t="str">
-        <v>London, United Kingdom</v>
+        <v>United States</v>
       </c>
       <c r="J56" t="str">
-        <v>https://www.exploretalent.com/auditions/1672970</v>
+        <v>https://www.exploretalent.com/auditions/1674531</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57">
-        <v>1672880</v>
+        <v>1673716</v>
       </c>
       <c r="B57" t="str">
-        <v>Nike Jordan Commercial Casting Call</v>
+        <v>Phone Company Commercial Casting Call for Dancers</v>
       </c>
       <c r="C57" t="str">
-        <v>2000.00/ day</v>
+        <v>2500.00/ event</v>
       </c>
       <c r="D57" t="str" xml:space="preserve">
-        <v xml:space="preserve">NYC photo/video shoot seeks real friend groups and individuals embodying street culture, style, and youthful energy for a major athletic brand. The campaign celebrates diversity, creativity, and unique personalities, showcasing confidence for a global sportswear brand.
+        <v xml:space="preserve">Seattle shoot seeks a skilled male breakdancer (ages 20-80) for a phone company commercial. This is a great opportunity for a talented dancer to showcase their skills and work with a professional team.
 </v>
       </c>
       <c r="E57" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F57" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G57" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672880/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673716/edit</v>
       </c>
       <c r="H57" t="str">
-        <v>06/14/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I57" t="str">
-        <v>New York, United States</v>
+        <v>Miami, Florida</v>
       </c>
       <c r="J57" t="str">
-        <v>https://www.exploretalent.com/auditions/1672880</v>
+        <v>https://www.exploretalent.com/auditions/1673716</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
       <c r="A58">
-        <v>1672195</v>
+        <v>1674787</v>
       </c>
       <c r="B58" t="str">
-        <v>$2,000 Japanese TV Commercial Casting Call for Human Statue Performers</v>
+        <v>Demi Lovato Music Video Casting</v>
       </c>
       <c r="C58" t="str">
-        <v>2000.00/ event</v>
+        <v>2350.00/ day</v>
       </c>
       <c r="D58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Skilled human statue performers needed for a Japanese TV commercial. One-day shoot requires excellent body control, own costume/makeup, and ability to maintain stillness. Experience preferred.
+        <v xml:space="preserve">Demi Lovato's music video seeks diverse SAG/non-union talent for stills and motion. Directed by Daniel Sachon with creative direction by Imogene, the project requires cinematic individuals of all ages, ethnicities, body types, and identities.
 </v>
       </c>
       <c r="E58" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F58" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G58" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672195/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674787/edit</v>
       </c>
       <c r="H58" t="str">
-        <v>06/30/2025</v>
+        <v>07/24/2025</v>
       </c>
       <c r="I58" t="str">
-        <v>Australia</v>
+        <v>Los Angeles</v>
       </c>
       <c r="J58" t="str">
-        <v>https://www.exploretalent.com/auditions/1672195</v>
+        <v>https://www.exploretalent.com/auditions/1674787</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59">
-        <v>1672929</v>
+        <v>1673182</v>
       </c>
       <c r="B59" t="str">
-        <v>Disneyland Commercial Casting Call for Siblings</v>
+        <v>Adidas Commercial Casting Call</v>
       </c>
       <c r="C59" t="str">
-        <v>1800.00/ event</v>
+        <v>2250.00/ event</v>
       </c>
       <c r="D59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Adult siblings are needed for a Disneyland commercial highlighting lasting memories and sibling bonds. The one-day shoot involves enjoying park activities while capturing genuine moments of joy and nostalgia, representing the magic of shared childhood experiences.
+        <v xml:space="preserve">Major commercial campaign casting diverse male and female actors/models, ages 20-45, for various roles. This one-day shoot offers great visibility. Talent must be professional, prepared to portray diverse characters in scripted or lifestyle scenes, and follow direction.
 </v>
       </c>
       <c r="E59" t="str">
-        <v>1 - 80</v>
+        <v>20 - 45</v>
       </c>
       <c r="F59" t="str">
         <v>Any</v>
       </c>
       <c r="G59" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672929/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673182/edit</v>
       </c>
       <c r="H59" t="str">
-        <v>06/13/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I59" t="str">
-        <v>Los Angeles, California</v>
+        <v>United States</v>
       </c>
       <c r="J59" t="str">
-        <v>https://www.exploretalent.com/auditions/1672929</v>
+        <v>https://www.exploretalent.com/auditions/1673182</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60">
-        <v>1672928</v>
+        <v>1674378</v>
       </c>
       <c r="B60" t="str">
-        <v>Disneyland Commercial Casting Call for Disneybounders</v>
+        <v>Spirits Commercial Casting OCP Female Talent</v>
       </c>
       <c r="C60" t="str">
-        <v>1800.00/ event</v>
+        <v>2250.00/ event</v>
       </c>
       <c r="D60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Disney fans with creative, themed looks are wanted for a commercial shoot at Disneyland. Show off your Disneybound style and personal flair on camera in a high-energy campaign celebrating fashion and fandom. Be featured in segments highlighting your creativity and love for Disney fashion.
+        <v xml:space="preserve">OCP female talent needed for a spirits commercial. Must embody warmth, charm, and approachability with an expressive smile and engaging presence. The role requires natural on-camera expressions, collaboration with the crew, and professionalism to highlight product moments authentically.
 </v>
       </c>
       <c r="E60" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F60" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G60" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672928/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674378/edit</v>
       </c>
       <c r="H60" t="str">
-        <v>06/13/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="I60" t="str">
-        <v>Los Angeles</v>
+        <v>United States</v>
       </c>
       <c r="J60" t="str">
-        <v>https://www.exploretalent.com/auditions/1672928</v>
+        <v>https://www.exploretalent.com/auditions/1674378</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61">
-        <v>1672925</v>
+        <v>1674377</v>
       </c>
       <c r="B61" t="str">
-        <v>Disneyland Commercial Casting Call for Friend Groups and Families</v>
+        <v>Spirits Commercial Casting Call for Male Bartender</v>
       </c>
       <c r="C61" t="str">
-        <v>1800.00/ event</v>
+        <v>2250.00/ event</v>
       </c>
       <c r="D61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Be in a Disneyland commercial! Real friend groups and families are needed for a one-day shoot showcasing authentic joy and unforgettable memories in the park. Represent the magic of friendship and family fun in a Disney setting.
+        <v xml:space="preserve">Seeking a stylish Latin male bartender for a commercial. Must have expert mixology skills, a charming presence, and be able to perform dynamic bartending actions. The role requires engaging with the camera, collaborating with the director, and working well with the production team.
 </v>
       </c>
       <c r="E61" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F61" t="str">
         <v>Any</v>
       </c>
       <c r="G61" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672925/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674377/edit</v>
       </c>
       <c r="H61" t="str">
-        <v>06/13/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="I61" t="str">
-        <v>Los Angeles, California</v>
+        <v>United States</v>
       </c>
       <c r="J61" t="str">
-        <v>https://www.exploretalent.com/auditions/1672925</v>
+        <v>https://www.exploretalent.com/auditions/1674377</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
       <c r="A62">
-        <v>1672752</v>
+        <v>1673384</v>
       </c>
       <c r="B62" t="str">
-        <v>Disneyland Commercial Casting Call for Super Fans</v>
+        <v>Commercial Casting Call for Construction Workers</v>
       </c>
       <c r="C62" t="str">
-        <v>1800.00/ event</v>
+        <v>2250.00/ event</v>
       </c>
       <c r="D62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Disney, Marvel, Star Wars, and Pixar superfans are wanted for a paid Disneyland commercial shoot. Families and friend groups can showcase their love for these franchises and the magic of Disneyland on screen.
+        <v xml:space="preserve">National campaign seeks authentic male and female construction workers with heavy machinery experience (loaders, etc.) from quarries, mines, or industrial sites. High pay for gritty, skilled individuals to portray their profession in print, web, and video ads.
 </v>
       </c>
       <c r="E62" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F62" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G62" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672752/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673384/edit</v>
       </c>
       <c r="H62" t="str">
-        <v>06/16/2025</v>
+        <v>07/05/2025</v>
       </c>
       <c r="I62" t="str">
-        <v>Anaheim, California</v>
+        <v>Austin, Texas</v>
       </c>
       <c r="J62" t="str">
-        <v>https://www.exploretalent.com/auditions/1672752</v>
+        <v>https://www.exploretalent.com/auditions/1673384</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63">
-        <v>1672748</v>
+        <v>1674534</v>
       </c>
       <c r="B63" t="str">
-        <v>$1,800 Disneyland Commercial Casting Call for Older Couples</v>
+        <v>Casting Models for PUMA Campaign</v>
       </c>
       <c r="C63" t="str">
-        <v>1800.00/ event</v>
+        <v>2200.00/ event</v>
       </c>
       <c r="D63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Disneyland's 70th anniversary commercial seeks real couples (65+) with genuine warmth and Disney stories. This paid opportunity celebrates generations of park guests in a joyful, nostalgic production.
+        <v xml:space="preserve">PUMA seeks diverse models (18-80) for a 1-year global campaign. The shoot includes stills and video for in-store, e-commerce, PR, social media, and PUMA's digital channels. Local talent preferred; submit unfiltered photos showcasing look and style.
 </v>
       </c>
       <c r="E63" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F63" t="str">
         <v>Any</v>
       </c>
       <c r="G63" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672748/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674534/edit</v>
       </c>
       <c r="H63" t="str">
-        <v>06/16/2025</v>
+        <v>06/28/2025</v>
       </c>
       <c r="I63" t="str">
-        <v>Anaheim, California</v>
+        <v>New York, NY, United States</v>
       </c>
       <c r="J63" t="str">
-        <v>https://www.exploretalent.com/auditions/1672748</v>
+        <v>https://www.exploretalent.com/auditions/1674534</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
       <c r="A64">
-        <v>1672579</v>
+        <v>1674476</v>
       </c>
       <c r="B64" t="str">
-        <v>Liquor Brand Photo Shoot Casting Call for Models</v>
+        <v>Mitsubishi Outlander Commercial Casting Call</v>
       </c>
       <c r="C64" t="str">
-        <v>1800.00/ day</v>
+        <v>2100.00/ event</v>
       </c>
       <c r="D64" t="str" xml:space="preserve">
-        <v xml:space="preserve">A liquor brand seeks diverse, confident talent for a high-end lifestyle photoshoot. The campaign aims to capture stylish, inclusive visuals in a vibrant, social setting. Talent should bring natural energy, style, and authenticity to represent the brand confidently in still photography.
+        <v xml:space="preserve">Mitsubishi seeks real Outlander PHEV owners to share their stories in a national commercial. If the SUV fits your lifestyle and you're comfortable on camera, apply! No acting experience needed. Selected drivers will participate in a virtual call and a one-day shoot.
 </v>
       </c>
       <c r="E64" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F64" t="str">
         <v>Any</v>
       </c>
       <c r="G64" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672579/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674476/edit</v>
       </c>
       <c r="H64" t="str">
-        <v>06/22/2025</v>
+        <v>07/19/2025</v>
       </c>
       <c r="I64" t="str">
-        <v>Pennsylvania</v>
+        <v>Canada</v>
       </c>
       <c r="J64" t="str">
-        <v>https://www.exploretalent.com/auditions/1672579</v>
+        <v>https://www.exploretalent.com/auditions/1674476</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65">
-        <v>1672227</v>
+        <v>1673736</v>
       </c>
       <c r="B65" t="str">
-        <v>Multi-Talented Performers Wanted for Long-Term Resort Residency</v>
+        <v>Dove Campaign Casting Track &amp; Field Athletes</v>
       </c>
       <c r="C65" t="str">
-        <v>1800.00/ month</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Multi-talented performers wanted for a high-energy residency at a luxury resort. Showcase specialty acts in five daily shows, collaborating with an international team. Requires strong stage presence, quick changes, and prior experience. Shared accommodation and meals provided. Seeking energetic, creative, and collaborative individuals.
+        <v xml:space="preserve">Dove is casting real teen female track and field athletes for a national campaign celebrating authenticity, athleticism, and confidence. No experience needed, just genuine athletes ready to share their stories and represent themselves naturally on camera.
 </v>
       </c>
       <c r="E65" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F65" t="str">
         <v>Any</v>
       </c>
       <c r="G65" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672227/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673736/edit</v>
       </c>
       <c r="H65" t="str">
-        <v>06/06/2025</v>
+        <v>07/10/2025</v>
       </c>
       <c r="I65" t="str">
-        <v>South Korea</v>
+        <v>Ontario, Canada</v>
       </c>
       <c r="J65" t="str">
-        <v>https://www.exploretalent.com/auditions/1672227</v>
+        <v>https://www.exploretalent.com/auditions/1673736</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66">
-        <v>1672226</v>
+        <v>1673133</v>
       </c>
       <c r="B66" t="str">
-        <v>Magician for Long-Term Resort Stage Shows</v>
+        <v>Dove Campaign Casting Call: Teen Athletes</v>
       </c>
       <c r="C66" t="str">
-        <v>1800.00/ month</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Luxury resort seeks a charismatic magician for a long-term residency. Perform five daily shows (close-up, fire, stage illusions) for international audiences. Requires proven experience, adaptability, and relocation. Offers $1,800/month, free accommodation, meals, costumes, and collaboration with a diverse creative team.
+        <v xml:space="preserve">Casting teenage girls (14-17) in competitive team sports for a national campaign celebrating young female athletes. Seeking authentic, diverse teens to represent their sport and share their experiences on camera, individually or with their team. No actors or models.
 </v>
       </c>
       <c r="E66" t="str">
-        <v>1 - 80</v>
+        <v>14 - 17</v>
       </c>
       <c r="F66" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G66" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672226/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673133/edit</v>
       </c>
       <c r="H66" t="str">
-        <v>06/06/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="I66" t="str">
-        <v>South Korea</v>
+        <v>Canada</v>
       </c>
       <c r="J66" t="str">
-        <v>https://www.exploretalent.com/auditions/1672226</v>
+        <v>https://www.exploretalent.com/auditions/1673133</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67">
-        <v>1672843</v>
+        <v>1674826</v>
       </c>
       <c r="B67" t="str">
-        <v>Commercial Casting Call for Mom</v>
+        <v>Diaper Brand Commercial Casting Call for Babies</v>
       </c>
       <c r="C67" t="str">
-        <v>1600.00/ event</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Commercial seeks a warm, maternal actress for a non-speaking role. Must have a nurturing presence and on-camera confidence. Real moms, especially with children aged 5-8, are encouraged to apply for potential parent-child interaction. The role involves portraying a loving mother figure and following direction.
+        <v xml:space="preserve">A diaper brand seeks preemie, newborn, and twin babies for a commercial photo shoot. This opportunity allows parents to showcase their infants' authentic expressions and tiny details in a professional campaign, highlighting real-life early parenting moments. Participation includes the shoot and a pre-shoot fitting.
 </v>
       </c>
       <c r="E67" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F67" t="str">
         <v>Any</v>
       </c>
       <c r="G67" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672843/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674826/edit</v>
       </c>
       <c r="H67" t="str">
-        <v>06/15/2025</v>
+        <v>07/26/2025</v>
       </c>
       <c r="I67" t="str">
-        <v>Nashville, Tennessee</v>
+        <v>Los Angeles, California</v>
       </c>
       <c r="J67" t="str">
-        <v>https://www.exploretalent.com/auditions/1672843</v>
+        <v>https://www.exploretalent.com/auditions/1674826</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68">
-        <v>1672228</v>
+        <v>1674781</v>
       </c>
       <c r="B68" t="str">
-        <v>Latin Dance Couple for Luxury Resort Performances</v>
+        <v>Casting for Global Professional Services Campaign</v>
       </c>
       <c r="C68" t="str">
-        <v>1500.00/ month</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Talented Latin dance couples wanted for a long-term resort residency. Showcase your passion and precision in high-energy performances blending salsa, tango, cha-cha, and influences from jazz, pop, and ballet. Join an international team!
+        <v xml:space="preserve">Global campaign seeks diverse, authentic individuals (ages 3-80) to portray modern professionals in a stills shoot. Must be comfortable on camera, exude warmth, and represent a range of lived experiences. The campaign celebrates diversity and confidence in smart, natural workplace settings.
 </v>
       </c>
       <c r="E68" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F68" t="str">
         <v>Any</v>
       </c>
       <c r="G68" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672228/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674781/edit</v>
       </c>
       <c r="H68" t="str">
-        <v>06/06/2025</v>
+        <v>07/24/2025</v>
       </c>
       <c r="I68" t="str">
-        <v>South Korea</v>
+        <v>United Kingdom</v>
       </c>
       <c r="J68" t="str">
-        <v>https://www.exploretalent.com/auditions/1672228</v>
+        <v>https://www.exploretalent.com/auditions/1674781</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69">
-        <v>1673156</v>
+        <v>1674517</v>
       </c>
       <c r="B69" t="str">
-        <v>Social Media Campaign Los Angeles Casting Call for Drummers</v>
+        <v>Girl Drummers Casting Call for Software Commercial</v>
       </c>
       <c r="C69" t="str">
-        <v>1500.00/ day</v>
+        <v>2000.00/ day</v>
       </c>
       <c r="D69" t="str" xml:space="preserve">
-        <v xml:space="preserve">A social media campaign seeks Gen Z drummers for a paid, one-day shoot. Local talent passionate about drumming will create dynamic digital content celebrating rhythm, authenticity, and personal passion.
+        <v xml:space="preserve">A software brand seeks young female drummers (beginner-intermediate) for a commercial. Performers will play simple patterns, sync to cues, and interact naturally. Mothers can join. Rehearsal, wardrobe, drums, and meals provided. Professional footage for reels.
 </v>
       </c>
       <c r="E69" t="str">
-        <v>1 - 80</v>
+        <v>5 - 80</v>
       </c>
       <c r="F69" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G69" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673156/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674517/edit</v>
       </c>
       <c r="H69" t="str">
-        <v>07/03/2025</v>
+        <v>07/21/2025</v>
       </c>
       <c r="I69" t="str">
-        <v>Los Angeles, California</v>
+        <v>Florida</v>
       </c>
       <c r="J69" t="str">
-        <v>https://www.exploretalent.com/auditions/1673156</v>
+        <v>https://www.exploretalent.com/auditions/1674517</v>
       </c>
     </row>
     <row r="70" xml:space="preserve">
       <c r="A70">
-        <v>1673079</v>
+        <v>1674513</v>
       </c>
       <c r="B70" t="str">
-        <v>Nationwide Voiceover Casting Call - Female Voice</v>
+        <v>Casting Call for Salsa Dancers in Sydney Commercial</v>
       </c>
       <c r="C70" t="str">
-        <v>1500.00/ event</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Non-union female voice actor needed for a national commercial campaign. Deliver a dynamic, warm, and humorous performance with clear, high-energy vocals. Remote recording accepted. Must embody the character with enthusiasm and meet quality standards. Paid opportunity.
+        <v xml:space="preserve">Sydney commercial seeks confident older adults with salsa dancing experience (social or class-based). All skill levels and body types are welcome to perform energetic moves, take direction, and showcase joyful expressions. Professional credit and footage provided for this one-day shoot.
 </v>
       </c>
       <c r="E70" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F70" t="str">
         <v>Any</v>
       </c>
       <c r="G70" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673079/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674513/edit</v>
       </c>
       <c r="H70" t="str">
-        <v>06/09/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I70" t="str">
-        <v>United States</v>
+        <v>Australia</v>
       </c>
       <c r="J70" t="str">
-        <v>https://www.exploretalent.com/auditions/1673079</v>
+        <v>https://www.exploretalent.com/auditions/1674513</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71">
-        <v>1673078</v>
+        <v>1674376</v>
       </c>
       <c r="B71" t="str">
-        <v>Celsius Voiceover Nationwide Casting Call - Cory</v>
+        <v>Spirits Commercial Casting Call for Female Friend</v>
       </c>
       <c r="C71" t="str">
-        <v>1500.00/ event</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Miami Talent Casting seeks a male voice actor for a national commercial. The role is Cory, a clever, high-energy character in his mid-to-late 20s. Non-union talent with a sharp, clear, and expressive voice, embodying mindfulness, intelligence, and humor, are encouraged to apply for this remote job.
+        <v xml:space="preserve">Seeking a trendy, social female (25-80) to play the lead's close friend in a commercial. The role requires lively banter, showcasing branded moments, spontaneous reactions, and maintaining high energy through vibrant movement and expressions, all while collaborating with the team.
 </v>
       </c>
       <c r="E71" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F71" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G71" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673078/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674376/edit</v>
       </c>
       <c r="H71" t="str">
-        <v>06/09/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="I71" t="str">
-        <v>N/A</v>
+        <v>United States</v>
       </c>
       <c r="J71" t="str">
-        <v>https://www.exploretalent.com/auditions/1673078</v>
+        <v>https://www.exploretalent.com/auditions/1674376</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
       <c r="A72">
-        <v>1673077</v>
+        <v>1674347</v>
       </c>
       <c r="B72" t="str">
-        <v>Bilingual Voiceover Casting Call - Alex</v>
+        <v>Voiceover Talent for Cyber Security Software</v>
       </c>
       <c r="C72" t="str">
-        <v>1500.00/ event</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Commercial campaign seeks a bilingual (English/Spanish) male voice actor, early to mid-30s, for Alex, a Latin American father and firefighter. Must have a warm, sincere, strong voice with a Spanish accent in English, conveying depth, relatability, and natural energy. Textured vocal tones preferred. Paid opportunity.
+        <v xml:space="preserve">Cybersecurity software project seeks male and female voiceover talent (ages 3-80). Applicants must have access to a home or professional recording studio for the session.
 </v>
       </c>
       <c r="E72" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F72" t="str">
         <v>Any</v>
       </c>
       <c r="G72" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673077/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674347/edit</v>
       </c>
       <c r="H72" t="str">
-        <v>06/09/2025</v>
+        <v>07/01/2025</v>
       </c>
       <c r="I72" t="str">
-        <v>N/A</v>
+        <v>United States</v>
       </c>
       <c r="J72" t="str">
-        <v>https://www.exploretalent.com/auditions/1673077</v>
+        <v>https://www.exploretalent.com/auditions/1674347</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73">
-        <v>1672881</v>
+        <v>1673307</v>
       </c>
       <c r="B73" t="str">
-        <v>Hard Surface Flooring Commercial Casting Call</v>
+        <v>Golf Experience Commercial Casting Real Father and Son</v>
       </c>
       <c r="C73" t="str">
-        <v>1500.00/ day</v>
+        <v>2000.00/ day</v>
       </c>
       <c r="D73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking experienced DIYers for a commercial photo/video shoot for an international flooring brand. Talent must be comfortable on camera, skilled in flooring installation and tool usage, and able to follow direction for dynamic, real-world action shots in a professional setting.
+        <v xml:space="preserve">A real father and son are needed for a one-day golf shoot. The production seeks authentic chemistry and natural interactions between the pair on a scenic golf course. Participants must be punctual, professional, and follow simple directions.
 </v>
       </c>
       <c r="E73" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F73" t="str">
         <v>Any</v>
       </c>
       <c r="G73" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672881/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673307/edit</v>
       </c>
       <c r="H73" t="str">
-        <v>06/14/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I73" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Australia</v>
       </c>
       <c r="J73" t="str">
-        <v>https://www.exploretalent.com/auditions/1672881</v>
+        <v>https://www.exploretalent.com/auditions/1673307</v>
       </c>
     </row>
     <row r="74" xml:space="preserve">
       <c r="A74">
-        <v>1672756</v>
+        <v>1673205</v>
       </c>
       <c r="B74" t="str">
-        <v>Farm Commercial Casting Call</v>
+        <v>Global Services Campaign Casting Call</v>
       </c>
       <c r="C74" t="str">
-        <v>1500.00/ day</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a charismatic, local Tennessee male actor for a family-friendly farm commercial. The "Agent" role requires a professional, approachable demeanor to interact with Smokey Bear. Must have a strong screen presence, clean-cut look, and regional authenticity.
+        <v xml:space="preserve">A global campaign seeks real people (18-70, any ethnicity) with confidence and compelling stories to portray modern professionals in a one-day photo shoot. No prior experience needed, just a professional appearance and natural energy in business/smart casual attire. Background checks required.
 </v>
       </c>
       <c r="E74" t="str">
-        <v>1 - 80</v>
+        <v>18 - 70</v>
       </c>
       <c r="F74" t="str">
         <v>Any</v>
       </c>
       <c r="G74" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672756/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673205/edit</v>
       </c>
       <c r="H74" t="str">
-        <v>06/16/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I74" t="str">
-        <v>United States</v>
+        <v>United Kingdom</v>
       </c>
       <c r="J74" t="str">
-        <v>https://www.exploretalent.com/auditions/1672756</v>
+        <v>https://www.exploretalent.com/auditions/1673205</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75">
-        <v>1672230</v>
+        <v>1672970</v>
       </c>
       <c r="B75" t="str">
-        <v>Female Dancer Needed for Live Resort Entertainment</v>
+        <v>Insurance Advert Commercial Casting Call</v>
       </c>
       <c r="C75" t="str">
-        <v>1500.00/ month</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Experienced Christmas light decorators are wanted nationwide for a TV show. Families/communities with extraordinary, large-scale displays incorporating music, animation, and creative design can compete for a $50,000 prize. Share your holiday magic with America!
+        <v xml:space="preserve">Real couples (65-70) are wanted for an insurance commercial. Non-actors who naturally convey connection will be filmed in a lifestyle setting. The shoot includes a brand-paid mini-break in France. Content will be used online and on social media.
 </v>
       </c>
       <c r="E75" t="str">
-        <v>1 - 80</v>
+        <v>65 - 70</v>
       </c>
       <c r="F75" t="str">
         <v>Any</v>
       </c>
       <c r="G75" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672230/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672970/edit</v>
       </c>
       <c r="H75" t="str">
-        <v>06/06/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="I75" t="str">
-        <v>South Korea</v>
+        <v>London, United Kingdom</v>
       </c>
       <c r="J75" t="str">
-        <v>https://www.exploretalent.com/auditions/1672230</v>
+        <v>https://www.exploretalent.com/auditions/1672970</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
       <c r="A76">
-        <v>1673016</v>
+        <v>1672342</v>
       </c>
       <c r="B76" t="str">
-        <v>Casting: Female Stunt Performers</v>
+        <v>New Orleans Casting Call for Female Law Enforcement or Military Talent</v>
       </c>
       <c r="C76" t="str">
-        <v>1465.00/ month</v>
+        <v>2000.00/ day</v>
       </c>
       <c r="D76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking confident female performers for a 3-month Morocco residency. Performers will star in dynamic evening shows for international audiences, utilizing freestyle, choreography, and special skills. Must maintain high energy, professionalism, and participate in rehearsals.
+        <v xml:space="preserve">Casting a female (30-50) with authentic police/military background for a well-paid role as a law enforcement professional. Requires a commanding presence, realistic portrayal, and ability to confidently follow direction. Non-union only.
 </v>
       </c>
       <c r="E76" t="str">
-        <v>1 - 80</v>
+        <v>30 - 50</v>
       </c>
       <c r="F76" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G76" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673016/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672342/edit</v>
       </c>
       <c r="H76" t="str">
-        <v>06/09/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I76" t="str">
-        <v>Morocco</v>
+        <v>New Orleans, Louisiana</v>
       </c>
       <c r="J76" t="str">
-        <v>https://www.exploretalent.com/auditions/1673016</v>
+        <v>https://www.exploretalent.com/auditions/1672342</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
       <c r="A77">
-        <v>1672788</v>
+        <v>1672324</v>
       </c>
       <c r="B77" t="str">
-        <v>Dairy Products Commercial Casting Call</v>
+        <v>International Mobile Phone Commercial Casting Call for Male Podcast Host Jordan</v>
       </c>
       <c r="C77" t="str">
-        <v>1250.00/ event</v>
+        <v>2000.00/ negotiable</v>
       </c>
       <c r="D77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking energetic, quirky child actors for a dairy commercial. Must be outgoing and chatty to bring genuine personality. Home shoot, meals/expenses covered, licensing provided. Great opportunity for experience and exposure.
+        <v xml:space="preserve">Casting "Jordan," a sharp, articulate male podcast host (20-30) with a natural conversational gift and thoughtful personality. Must have a strong presence, excellent English, and represent a modern brand. Filming in Bangkok.
 </v>
       </c>
       <c r="E77" t="str">
-        <v>1 - 80</v>
+        <v>20 - 30</v>
       </c>
       <c r="F77" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G77" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672788/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672324/edit</v>
       </c>
       <c r="H77" t="str">
-        <v>06/16/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="I77" t="str">
-        <v>London, United Kingdom</v>
+        <v>N/A</v>
       </c>
       <c r="J77" t="str">
-        <v>https://www.exploretalent.com/auditions/1672788</v>
+        <v>https://www.exploretalent.com/auditions/1672324</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
       <c r="A78">
-        <v>1672690</v>
+        <v>1672195</v>
       </c>
       <c r="B78" t="str">
-        <v>Dairy Products Commercial Casting Call for Siblings</v>
+        <v>$2,000 Japanese TV Commercial Casting Call for Human Statue Performers</v>
       </c>
       <c r="C78" t="str">
-        <v>1250.00/ event</v>
+        <v>2000.00/ event</v>
       </c>
       <c r="D78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dairy commercial casting real siblings/friends (9-10). Seeking chatty, authentic, quirky kids with standout personalities for a fun, energetic shoot. Great opportunity for commercial experience.
+        <v xml:space="preserve">Japanese TV commercial seeks a human statue performer for a one-day shoot. Ideal candidates possess excellent body control, stillness, and performance art experience. Performers must provide their own costume and makeup and follow the director's vision. This is a high-profile international project.
 </v>
       </c>
       <c r="E78" t="str">
-        <v>1 - 80</v>
+        <v>0 - 100</v>
       </c>
       <c r="F78" t="str">
         <v>Any</v>
       </c>
       <c r="G78" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672690/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672195/edit</v>
       </c>
       <c r="H78" t="str">
-        <v>06/19/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I78" t="str">
-        <v>London, United Kingdom</v>
+        <v>Australia</v>
       </c>
       <c r="J78" t="str">
-        <v>https://www.exploretalent.com/auditions/1672690</v>
+        <v>https://www.exploretalent.com/auditions/1672195</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
       <c r="A79">
-        <v>1672350</v>
+        <v>1673654</v>
       </c>
       <c r="B79" t="str">
-        <v>Diwali Commercial Casting Call for Southeast Asian or Indian Mother</v>
+        <v>Sally Beauty Commercial Casting Call</v>
       </c>
       <c r="C79" t="str">
-        <v>1250.00/ event</v>
+        <v>1750.00/ event</v>
       </c>
       <c r="D79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Commercial seeks a Southeast Asian/Indian, non-union female actor (30-43) in the Greater Boston area to portray a mother in a Diwali scene. The role involves sharing Diwali traditions in festive attire for a national campaign. Submit a video introducing yourself and explaining how your family celebrates Diwali.
+        <v xml:space="preserve">A national beauty brand seeks female models/actors (20-80) for a high-profile commercial/campaign. The project celebrates beauty, confidence, and individuality. Talent should embody the brand's spirit with charisma and authenticity. Multiple paid bookings offer industry exposure.
 </v>
       </c>
       <c r="E79" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F79" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G79" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672350/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673654/edit</v>
       </c>
       <c r="H79" t="str">
-        <v>06/30/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I79" t="str">
-        <v>Boston, Massachusetts</v>
+        <v>United States</v>
       </c>
       <c r="J79" t="str">
-        <v>https://www.exploretalent.com/auditions/1672350</v>
+        <v>https://www.exploretalent.com/auditions/1673654</v>
       </c>
     </row>
     <row r="80" xml:space="preserve">
       <c r="A80">
-        <v>1672349</v>
+        <v>1674502</v>
       </c>
       <c r="B80" t="str">
-        <v>Diwali Commercial Casting Call for Southeast Asian or Indian Child</v>
+        <v>Grocery Store Commercial Casting Call</v>
       </c>
       <c r="C80" t="str">
-        <v>1250.00/ event</v>
+        <v>1700.00/ event</v>
       </c>
       <c r="D80" t="str" xml:space="preserve">
-        <v xml:space="preserve">A national commercial seeks a Southeast Asian or Indian girl (7-9) in the Greater Boston area to portray a daughter celebrating Diwali. The non-union role requires a short video showcasing Diwali traditions. Paid opportunity.
+        <v xml:space="preserve">A Texas grocery brand seeks diverse kids (5-17) for a San Antonio TV spot. The upbeat, inclusive classroom scene requires talent comfortable on camera, able to follow direction, and maintain positive energy during takes. One-day shoot.
 </v>
       </c>
       <c r="E80" t="str">
-        <v>1 - 80</v>
+        <v>5 - 80</v>
       </c>
       <c r="F80" t="str">
         <v>Any</v>
       </c>
       <c r="G80" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672349/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674502/edit</v>
       </c>
       <c r="H80" t="str">
-        <v>06/30/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I80" t="str">
-        <v>Boston, Massachusetts</v>
+        <v>San Antonio, Texas</v>
       </c>
       <c r="J80" t="str">
-        <v>https://www.exploretalent.com/auditions/1672349</v>
+        <v>https://www.exploretalent.com/auditions/1674502</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
       <c r="A81">
-        <v>1672348</v>
+        <v>1674808</v>
       </c>
       <c r="B81" t="str">
-        <v>Diwali Commercial Casting Call for Southeast Asian/Indian Grandfather</v>
+        <v>Casting for Spotify Ad</v>
       </c>
       <c r="C81" t="str">
-        <v>1250.00/ event</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D81" t="str" xml:space="preserve">
-        <v xml:space="preserve">Commercial seeks a non-union Southeast Asian or Indian male actor (50-80) for a paid Diwali grandfather role. The actor will participate in a Diwali celebration scene, showcasing traditions. Submit a video introducing yourself and describing your family's Diwali celebrations.
+        <v xml:space="preserve">Spotify commercial casting seeks talent (18+) for a remote shoot. Submit self-tapes ASAP. Dates are TBD. Open to all ethnicities.
 </v>
       </c>
       <c r="E81" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F81" t="str">
         <v>Any</v>
       </c>
       <c r="G81" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672348/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674808/edit</v>
       </c>
       <c r="H81" t="str">
-        <v>06/30/2025</v>
+        <v>07/09/2025</v>
       </c>
       <c r="I81" t="str">
-        <v>Boston, Massachusetts</v>
+        <v>United States</v>
       </c>
       <c r="J81" t="str">
-        <v>https://www.exploretalent.com/auditions/1672348</v>
+        <v>https://www.exploretalent.com/auditions/1674808</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
       <c r="A82">
-        <v>1672924</v>
+        <v>1674494</v>
       </c>
       <c r="B82" t="str">
-        <v>Casting Call for Male Actors</v>
+        <v>Casting for Old Navy Commercial Shoot</v>
       </c>
       <c r="C82" t="str">
-        <v>1204.00/ day</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D82" t="str" xml:space="preserve">
-        <v xml:space="preserve">SAG-AFTRA project seeks male actors of all experience levels for roles demanding depth and authenticity. Union-scale work; professional materials required. Strong character development, presence, and reliability are valued.
+        <v xml:space="preserve">Old Navy is casting confident, stylish individuals of all backgrounds and experience levels for a new commercial. Models, influencers, and fashion enthusiasts are encouraged to apply, celebrating diversity and inclusivity.
 </v>
       </c>
       <c r="E82" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F82" t="str">
         <v>Any</v>
       </c>
       <c r="G82" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672924/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674494/edit</v>
       </c>
       <c r="H82" t="str">
-        <v>06/13/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="I82" t="str">
         <v>United States</v>
       </c>
       <c r="J82" t="str">
-        <v>https://www.exploretalent.com/auditions/1672924</v>
+        <v>https://www.exploretalent.com/auditions/1674494</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83">
-        <v>1672867</v>
+        <v>1674336</v>
       </c>
       <c r="B83" t="str">
-        <v>Tarot Card Reader Casting Call for Feature Film</v>
+        <v>Casting Now - Bold Singles</v>
       </c>
       <c r="C83" t="str">
-        <v>1204.00/ day</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Feature film seeks a real tarot reader for a one-day shoot in Massachusetts (May 27-July 2). Opportunity to showcase talent, perform a realistic reading on camera, and bring authentic, mystical energy to the scene. Collaboration with the production team is expected.
+        <v xml:space="preserve">A new dating show pilot is casting in LA, seeking models, influencers, creators, and tech bros (ages 21-35) for a luxury villa setting. Expect pool parties, startup drama, and romance. Auditions are filmed and unpaid, with potential for paid roles and brand collaborations later.
 </v>
       </c>
       <c r="E83" t="str">
-        <v>1 - 80</v>
+        <v>21 - 35</v>
       </c>
       <c r="F83" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G83" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672867/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674336/edit</v>
       </c>
       <c r="H83" t="str">
-        <v>06/14/2025</v>
+        <v>08/26/2025</v>
       </c>
       <c r="I83" t="str">
-        <v>United States</v>
+        <v>Las Vegas, NV&gt;Los Angeles, CA&gt;San Diego, CA</v>
       </c>
       <c r="J83" t="str">
-        <v>https://www.exploretalent.com/auditions/1672867</v>
+        <v>https://www.exploretalent.com/auditions/1674336</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
       <c r="A84">
-        <v>1672950</v>
+        <v>1674173</v>
       </c>
       <c r="B84" t="str">
-        <v>Fashion Campaign Casting</v>
+        <v>Casting for Psycho Bunny Print Shoot</v>
       </c>
       <c r="C84" t="str">
-        <v>1200.00/ event</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D84" t="str" xml:space="preserve">
-        <v xml:space="preserve">6397 fashion campaign casting seeks diverse, authentic talent of all ages and backgrounds. Models should embody elegance, energy, and effortless cool for lookbook, e-commerce, and B2B shoots. Must confidently represent the brand's vision and collaborate effectively with creative teams.
+        <v xml:space="preserve">Psycho Bunny seeks charismatic, confident individuals (ages 3-80) with a vibrant social life and elevated streetwear style. They should thrive in the spotlight and embody the brand's magnetic energy.
 </v>
       </c>
       <c r="E84" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F84" t="str">
         <v>Any</v>
       </c>
       <c r="G84" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672950/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674173/edit</v>
       </c>
       <c r="H84" t="str">
-        <v>07/02/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="I84" t="str">
-        <v>New York, United States</v>
+        <v>Miami, FL, United States</v>
       </c>
       <c r="J84" t="str">
-        <v>https://www.exploretalent.com/auditions/1672950</v>
+        <v>https://www.exploretalent.com/auditions/1674173</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
       <c r="A85">
-        <v>1672846</v>
+        <v>1674030</v>
       </c>
       <c r="B85" t="str">
-        <v>Casting Lead Models for High-Fashion Music Video Shoot</v>
+        <v>Casting for O.M.G Fashion Apparel Print Shoot</v>
       </c>
       <c r="C85" t="str">
-        <v>1200.00/ day</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D85" t="str" xml:space="preserve">
-        <v xml:space="preserve">Experienced models needed for a high-profile music video shoot in Miami. Showcase luxury fashion, collaborate with a creative team, and embody style and charisma on camera. A great opportunity for visibility.
+        <v xml:space="preserve">Fashion apparel print shoot seeking male/female models (18-80). Compensation, tear sheets, and video provided. Model release and potential NDA (due to celebrity backing) required. COVID restrictions may apply. Submit current, unedited photo and contact info.
 </v>
       </c>
       <c r="E85" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F85" t="str">
         <v>Any</v>
       </c>
       <c r="G85" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672846/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674030/edit</v>
       </c>
       <c r="H85" t="str">
-        <v>06/15/2025</v>
+        <v>06/28/2025</v>
       </c>
       <c r="I85" t="str">
-        <v>Miami</v>
+        <v>Los Angeles, CA, United States</v>
       </c>
       <c r="J85" t="str">
-        <v>https://www.exploretalent.com/auditions/1672846</v>
+        <v>https://www.exploretalent.com/auditions/1674030</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
       <c r="A86">
-        <v>1672793</v>
+        <v>1673647</v>
       </c>
       <c r="B86" t="str">
-        <v>Spa &amp; Body Scrub Product Line Commercial Casting Call</v>
+        <v>TV Commercial Casting for Bicycle Riders</v>
       </c>
       <c r="C86" t="str">
-        <v>1200.00/ event</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Become a print model for a skincare and body scrub brand's self-care campaign. Showcase spa and swimwear looks across web, social media, and in-store platforms. Seeking fresh, confident talent for this premium opportunity.
+        <v xml:space="preserve">Major TV commercial casting call for "MAMILs" (Middle-Aged Men in Lycra) aged 40-80. Seeking male bicycle riders comfortable on two wheels and confident on camera for a high-profile commercial.
 </v>
       </c>
       <c r="E86" t="str">
-        <v>1 - 80</v>
+        <v>40 - 80</v>
       </c>
       <c r="F86" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G86" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672793/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673647/edit</v>
       </c>
       <c r="H86" t="str">
-        <v>06/16/2025</v>
+        <v>07/06/2025</v>
       </c>
       <c r="I86" t="str">
-        <v>Austin, Texas</v>
+        <v>Australia</v>
       </c>
       <c r="J86" t="str">
-        <v>https://www.exploretalent.com/auditions/1672793</v>
+        <v>https://www.exploretalent.com/auditions/1673647</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
       <c r="A87">
-        <v>1672559</v>
+        <v>1674853</v>
       </c>
       <c r="B87" t="str">
-        <v>L'Oreal Beauty Commercial Casting</v>
+        <v>Fitness Brand Commercial Casting for Female Wellness Model</v>
       </c>
       <c r="C87" t="str">
-        <v>1200.00/ day</v>
+        <v>1500.00/ day</v>
       </c>
       <c r="D87" t="str" xml:space="preserve">
-        <v xml:space="preserve">Beauty brand casting African American women (30-45) with editorial modeling experience for a commercial celebrating natural beauty and diversity. Models must be confident, camera-ready, and available for a full-day shoot.
+        <v xml:space="preserve">A fitness brand seeks a female model (20-80) with a vibrant, positive personality and a balanced, fitness-focused lifestyle. The role involves showcasing authentic energy and wellness in a promotional video shoot.
 </v>
       </c>
       <c r="E87" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F87" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G87" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672559/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674853/edit</v>
       </c>
       <c r="H87" t="str">
-        <v>07/02/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I87" t="str">
-        <v>New York, United States</v>
+        <v>Australia</v>
       </c>
       <c r="J87" t="str">
-        <v>https://www.exploretalent.com/auditions/1672559</v>
+        <v>https://www.exploretalent.com/auditions/1674853</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
       <c r="A88">
-        <v>1672893</v>
+        <v>1674851</v>
       </c>
       <c r="B88" t="str">
-        <v>Casting Baseball Fans for a Major Professional Sports Team</v>
+        <v>Fitness Brand Commercial Casting for Male Model</v>
       </c>
       <c r="C88" t="str">
-        <v>1000.00/ day</v>
+        <v>1500.00/ day</v>
       </c>
       <c r="D88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Baseball fans wanted for a commercial directed by Nicolas Heller and a top ad agency! Show your passion for your team in this non-union project launching July 3rd. The campaign will be featured across digital, social, broadcast, and in-ballpark platforms.
+        <v xml:space="preserve">A fitness brand seeks a male model (25-80) with a muscular physique, warmth, and camera presence for a commercial. The shoot promotes strength, athletic dedication, and wellness. The model will confidently showcase strength and collaborate to create empowering, health-conscious visuals.
 </v>
       </c>
       <c r="E88" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F88" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G88" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672893/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674851/edit</v>
       </c>
       <c r="H88" t="str">
-        <v>06/13/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I88" t="str">
-        <v>New York, United States</v>
+        <v>Australia</v>
       </c>
       <c r="J88" t="str">
-        <v>https://www.exploretalent.com/auditions/1672893</v>
+        <v>https://www.exploretalent.com/auditions/1674851</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
       <c r="A89">
-        <v>1672775</v>
+        <v>1674850</v>
       </c>
       <c r="B89" t="str">
-        <v>Santa Maria Casting Call for Football Player</v>
+        <v>Fitness Brand Commercial Casting for Female Model</v>
       </c>
       <c r="C89" t="str">
-        <v>1000.00/ day</v>
+        <v>1500.00/ day</v>
       </c>
       <c r="D89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking male actors for a paid, featured background role in a 1970s-90s period drama. The scene depicts athletes celebrating a football victory in a locker room with full nudity. Confident performers with professionalism are required.
+        <v xml:space="preserve">Fitness brand seeks a confident, energetic female model (40-55, any ethnicity) for a health-focused weight loss campaign. The model should embody real wellness, body positivity, and inspire others with her strength and healthy lifestyle in a fitness video shoot.
 </v>
       </c>
       <c r="E89" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F89" t="str">
         <v>Any</v>
       </c>
       <c r="G89" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672775/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674850/edit</v>
       </c>
       <c r="H89" t="str">
-        <v>06/16/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I89" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Australia</v>
       </c>
       <c r="J89" t="str">
-        <v>https://www.exploretalent.com/auditions/1672775</v>
+        <v>https://www.exploretalent.com/auditions/1674850</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
       <c r="A90">
-        <v>1672742</v>
+        <v>1674749</v>
       </c>
       <c r="B90" t="str">
-        <v>Casting Baseball Fans for Commercial Spot</v>
+        <v>Casting: Veterans &amp; Active Service Members</v>
       </c>
       <c r="C90" t="str">
-        <v>1000.00/ event</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D90" t="str" xml:space="preserve">
-        <v xml:space="preserve">Energetic actors are needed for a paid national baseball commercial. They seek spirited, authentic fans with bold personalities and unique voices to bring their fan-like vibe to the camera. Showcase your talent in this fun, high-energy spot.
+        <v xml:space="preserve">Veterans/active-duty homeowners with mortgages are sought for a campaign. Share your story via self-recorded video and questionnaire. Selected participants will create follow-up videos, offering insights on homeownership and military service for potential national exposure.
 </v>
       </c>
       <c r="E90" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F90" t="str">
-        <v>Any</v>
+        <v>Male</v>
       </c>
       <c r="G90" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672742/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674749/edit</v>
       </c>
       <c r="H90" t="str">
-        <v>06/16/2025</v>
+        <v>07/24/2025</v>
       </c>
       <c r="I90" t="str">
-        <v>New York, United States</v>
+        <v>United States</v>
       </c>
       <c r="J90" t="str">
-        <v>https://www.exploretalent.com/auditions/1672742</v>
+        <v>https://www.exploretalent.com/auditions/1674749</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
       <c r="A91">
-        <v>1672670</v>
+        <v>1674430</v>
       </c>
       <c r="B91" t="str">
-        <v>$1,000 Energy Drink NYC Commercial Casting</v>
+        <v>Chicago Casting Call for Senior Commercial Roles</v>
       </c>
       <c r="C91" t="str">
-        <v>1000.00/ event</v>
+        <v>1500.00/ day</v>
       </c>
       <c r="D91" t="str" xml:space="preserve">
-        <v xml:space="preserve">NYC locals are wanted for featured roles in an energy drink commercial. This is a paid opportunity for commercial exposure. Submit a self-tape and headshot. Must be available for local shoots/fitting; no travel expenses covered.
+        <v xml:space="preserve">High-paying commercial roles for Asian, Hispanic/Latin, or Black seniors (65-80). Seeking authentic, comfortable on-camera talent for lifestyle/narrative scenes. One-day shoot, plus potential photoshoot. Opportunity to work on two major projects.
 </v>
       </c>
       <c r="E91" t="str">
-        <v>1 - 80</v>
+        <v>65 - 80</v>
       </c>
       <c r="F91" t="str">
         <v>Any</v>
       </c>
       <c r="G91" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672670/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674430/edit</v>
       </c>
       <c r="H91" t="str">
-        <v>06/18/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>Chicago, Illinois, United States</v>
       </c>
       <c r="J91" t="str">
-        <v>https://www.exploretalent.com/auditions/1672670</v>
+        <v>https://www.exploretalent.com/auditions/1674430</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
       <c r="A92">
-        <v>1672573</v>
+        <v>1673943</v>
       </c>
       <c r="B92" t="str">
-        <v>Jewelry Campaign Casting Call for Buzz Cut Woman in Ontario</v>
+        <v>Casting Real Recovery Stories for Awareness PSA</v>
       </c>
       <c r="C92" t="str">
-        <v>1000.00/ event</v>
+        <v>1500.00/ event</v>
       </c>
       <c r="D92" t="str" xml:space="preserve">
-        <v xml:space="preserve">A jewelry campaign seeks a woman to buzz her hair on camera in a barbershop. The powerful, authentic scene, filmed by a professional team, explores transformation, identity, and freedom. This paid role offers an additional $1,000 for the buzz cut.
+        <v xml:space="preserve">PSA campaign seeks actors and real people (18-80) with addiction/recovery connections to share honest stories, breaking stigma. Participants will engage in filmed testimonials or reenactments, portraying real-life experiences with empathy. The goal is awareness-driven storytelling through collaboration.
 </v>
       </c>
       <c r="E92" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F92" t="str">
         <v>Any</v>
       </c>
       <c r="G92" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672573/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673943/edit</v>
       </c>
       <c r="H92" t="str">
-        <v>06/30/2025</v>
+        <v>07/11/2025</v>
       </c>
       <c r="I92" t="str">
-        <v>Ontario</v>
+        <v>United States</v>
       </c>
       <c r="J92" t="str">
-        <v>https://www.exploretalent.com/auditions/1672573</v>
+        <v>https://www.exploretalent.com/auditions/1673943</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
       <c r="A93">
-        <v>1672308</v>
+        <v>1673156</v>
       </c>
       <c r="B93" t="str">
-        <v>Casting Real People for Documentary Series: Life in the City</v>
+        <v>Social Media Campaign Los Angeles Casting Call for Drummers</v>
       </c>
       <c r="C93" t="str">
-        <v>1000.00/ event</v>
+        <v>1500.00/ day</v>
       </c>
       <c r="D93" t="str" xml:space="preserve">
-        <v xml:space="preserve">A documentary series seeks diverse individuals (21+) in NYC, Chicago, Detroit, or Atlanta to share their authentic urban experiences. The unscripted project aims to break stereotypes and capture the reality of city life through interviews and filming, focusing on unique perspectives and personal journeys.
+        <v xml:space="preserve">Seeking passionate Gen Z drummers (18-28) for a branded social media campaign. Selected talent will share their drumming journey and perform on camera, guided by creative direction. This is a high-visibility opportunity to showcase your skills.
 </v>
       </c>
       <c r="E93" t="str">
-        <v>1 - 80</v>
+        <v>18 - 28</v>
       </c>
       <c r="F93" t="str">
         <v>Any</v>
       </c>
       <c r="G93" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672308/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673156/edit</v>
       </c>
       <c r="H93" t="str">
-        <v>06/27/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="I93" t="str">
-        <v>N/A</v>
+        <v>Los Angeles, California</v>
       </c>
       <c r="J93" t="str">
-        <v>https://www.exploretalent.com/auditions/1672308</v>
+        <v>https://www.exploretalent.com/auditions/1673156</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
       <c r="A94">
-        <v>1672200</v>
+        <v>1674505</v>
       </c>
       <c r="B94" t="str">
-        <v>Hair Models Needed for Premier Orlando Showcase</v>
+        <v>Rhonda Shear Commercial Casting Call</v>
       </c>
       <c r="C94" t="str">
-        <v>1000.00/ day</v>
+        <v>1400.00/ day</v>
       </c>
       <c r="D94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Curly haircare brand seeks female hair models for Premier Orlando. Models will receive professional styling with heat tools and be featured in live demos and educational sessions at this major beauty industry event, gaining significant exposure.
+        <v xml:space="preserve">Intimates brand seeks diverse female models (25-55) for a Florida product shoot. The campaign celebrates body positivity, showcasing lingerie, loungewear, and activewear for e-commerce, social media, and broadcast. Professional styling and meals provided.
 </v>
       </c>
       <c r="E94" t="str">
-        <v>1 - 80</v>
+        <v>25 - 80</v>
       </c>
       <c r="F94" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G94" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672200/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674505/edit</v>
       </c>
       <c r="H94" t="str">
-        <v>06/30/2025</v>
+        <v>07/20/2025</v>
       </c>
       <c r="I94" t="str">
-        <v>Orlando, Florida</v>
+        <v>Florida</v>
       </c>
       <c r="J94" t="str">
-        <v>https://www.exploretalent.com/auditions/1672200</v>
+        <v>https://www.exploretalent.com/auditions/1674505</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
       <c r="A95">
-        <v>1672176</v>
+        <v>1673214</v>
       </c>
       <c r="B95" t="str">
-        <v>Global Athletic Brand Live Event Hosts Ushers Greeters</v>
+        <v>Casting Call for Social Media Ad Featuring Disabled Teens</v>
       </c>
       <c r="C95" t="str">
-        <v>1000.00/ negotiable</v>
+        <v>1350.00/ event</v>
       </c>
       <c r="D95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking families/communities nationwide with spectacular Christmas light displays for a TV show. Participants should showcase massive, creative, and synchronized designs. The winner gets $50,000. Passionate decorators ready to share their holiday magic are encouraged to apply.
+        <v xml:space="preserve">Casting 14-19 year olds with disabilities whose lives have been positively impacted by social media. Seeking authentic stories of inspiration, community, or passion discovered online for a major social media platform's marketing campaign. All genders and ethnicities are encouraged to apply.
 </v>
       </c>
       <c r="E95" t="str">
-        <v>1 - 80</v>
+        <v>14 - 19</v>
       </c>
       <c r="F95" t="str">
         <v>Any</v>
       </c>
       <c r="G95" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672176/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1673214/edit</v>
       </c>
       <c r="H95" t="str">
-        <v>06/29/2025</v>
+        <v>07/04/2025</v>
       </c>
       <c r="I95" t="str">
-        <v>Los Angeles, California, United States</v>
+        <v>Nationwide</v>
       </c>
       <c r="J95" t="str">
-        <v>https://www.exploretalent.com/auditions/1672176</v>
+        <v>https://www.exploretalent.com/auditions/1673214</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
       <c r="A96">
-        <v>1672518</v>
+        <v>1672350</v>
       </c>
       <c r="B96" t="str">
-        <v>Global Wellness Brand Commercial Casting Call for New Yorkers – Lifestyle Campaign for Older Adults</v>
+        <v>Diwali Commercial Casting Call for Southeast Asian or Indian Mother</v>
       </c>
       <c r="C96" t="str">
-        <v>850.00/ day</v>
+        <v>1250.00/ event</v>
       </c>
       <c r="D96" t="str" xml:space="preserve">
-        <v xml:space="preserve">A wellness brand seeks charismatic individuals (55-80) for a NYC lifestyle shoot on June 1st or 2nd. The campaign celebrates confidence, individuality, and personal style, focusing on wellness and vitality. All ethnicities and body types are welcome; no experience needed.
+        <v xml:space="preserve">Commercial seeks a Southeast Asian or Indian female actor (30-43) to play a mother in a Diwali celebration. The role involves portraying warmth, sharing traditions, wearing festive attire, and engaging in family activities, offering authentic cultural representation.
 </v>
       </c>
       <c r="E96" t="str">
-        <v>1 - 80</v>
+        <v>30 - 43</v>
       </c>
       <c r="F96" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G96" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672518/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672350/edit</v>
       </c>
       <c r="H96" t="str">
-        <v>06/21/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="I96" t="str">
-        <v>New York</v>
+        <v>Boston, Massachusetts</v>
       </c>
       <c r="J96" t="str">
-        <v>https://www.exploretalent.com/auditions/1672518</v>
+        <v>https://www.exploretalent.com/auditions/1672350</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
       <c r="A97">
-        <v>1673139</v>
+        <v>1674079</v>
       </c>
       <c r="B97" t="str">
-        <v>Athletic Brand Commercial Casting Call</v>
+        <v>Casting Call for Anthony Bourdain Biopic</v>
       </c>
       <c r="C97" t="str">
-        <v>800.00/ day</v>
+        <v>1204.00/ day</v>
       </c>
       <c r="D97" t="str" xml:space="preserve">
-        <v xml:space="preserve">A major athletic brand seeks Gen Z talent for a paid commercial shoot. Fresh faces will portray confident, active lifestyles in a high-energy spot. Includes wardrobe fitting and a full-day shoot. Punctuality and professionalism are required for this high-visibility opportunity.
+        <v xml:space="preserve">A major film seeks a real Catholic priest from Portugal, fluent in European Portuguese, for a one-day shoot. The role requires portraying a priest authentically, bringing cultural depth to a pivotal scene in a high-profile biopic.
 </v>
       </c>
       <c r="E97" t="str">
-        <v>1 - 80</v>
+        <v>3 - 80</v>
       </c>
       <c r="F97" t="str">
         <v>Any</v>
       </c>
       <c r="G97" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673139/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674079/edit</v>
       </c>
       <c r="H97" t="str">
-        <v>07/03/2025</v>
+        <v>07/12/2025</v>
       </c>
       <c r="I97" t="str">
-        <v>New York</v>
+        <v>United States</v>
       </c>
       <c r="J97" t="str">
-        <v>https://www.exploretalent.com/auditions/1673139</v>
+        <v>https://www.exploretalent.com/auditions/1674079</v>
       </c>
     </row>
     <row r="98" xml:space="preserve">
       <c r="A98">
-        <v>1673021</v>
+        <v>1674688</v>
       </c>
       <c r="B98" t="str">
-        <v>Remitly Commercial Casting Call</v>
+        <v>Casting Call for Norwegian Cruise Line's 'Syd Norman's Pour House'</v>
       </c>
       <c r="C98" t="str">
-        <v>800.00/ day</v>
+        <v>1200.00/ week</v>
       </c>
       <c r="D98" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seeking a confident, fluent Punjabi-speaking actress for an on-camera commercial for a financial service brand. Must deliver clear, expressive Punjabi. Filming in Brooklyn, NY; travel covered.
+        <v xml:space="preserve">Norwegian Cruise Line seeks powerhouse vocalists and improv performers for "Syd Norman's Pour House," a high-energy, interactive rock show from the creators of Rock of Ages. The show celebrates classic rock from the '60s, '70s, and '80s, creating a rock 'n' roll party at sea.
 </v>
       </c>
       <c r="E98" t="str">
-        <v>1 - 80</v>
+        <v>20 - 80</v>
       </c>
       <c r="F98" t="str">
         <v>Any</v>
       </c>
       <c r="G98" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1673021/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674688/edit</v>
       </c>
       <c r="H98" t="str">
-        <v>06/09/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="I98" t="str">
-        <v>United States</v>
+        <v>Dublin, Ireland</v>
       </c>
       <c r="J98" t="str">
-        <v>https://www.exploretalent.com/auditions/1673021</v>
+        <v>https://www.exploretalent.com/auditions/1674688</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
       <c r="A99">
-        <v>1672927</v>
+        <v>1674415</v>
       </c>
       <c r="B99" t="str">
-        <v>$1,800 Disneyland Commercial Casting Call</v>
+        <v>Casting for Brandy Melville Fashion Campaign</v>
       </c>
       <c r="C99" t="str">
-        <v>800.00/ day</v>
+        <v>1200.00/ event</v>
       </c>
       <c r="D99" t="str" xml:space="preserve">
-        <v xml:space="preserve">Disneyland seeks U.S. military veteran/active service member families who love Disney, Marvel, Star Wars, or Pixar for a commercial. Share your family's Disney fandom and military pride during a one-day park shoot, capturing authentic, joyful moments.
+        <v xml:space="preserve">Brandy Melville is casting confident female talent (18-80) for a fashion campaign. No experience is needed, just comfort in front of the camera. This is a great opportunity to work with a well-known brand.
 </v>
       </c>
       <c r="E99" t="str">
-        <v>1 - 80</v>
+        <v>18 - 80</v>
       </c>
       <c r="F99" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G99" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672927/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1674415/edit</v>
       </c>
       <c r="H99" t="str">
-        <v>06/13/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="I99" t="str">
-        <v>Los Angeles, California</v>
+        <v>New York, NY, United States</v>
       </c>
       <c r="J99" t="str">
-        <v>https://www.exploretalent.com/auditions/1672927</v>
+        <v>https://www.exploretalent.com/auditions/1674415</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
       <c r="A100">
-        <v>1672926</v>
+        <v>1672559</v>
       </c>
       <c r="B100" t="str">
-        <v>Disneyland Commercial Casting Call for Kids</v>
+        <v>L'Oreal Beauty Commercial Casting</v>
       </c>
       <c r="C100" t="str">
-        <v>800.00/ day</v>
+        <v>1200.00/ day</v>
       </c>
       <c r="D100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Disneyland commercial seeks families with children newly tall enough for big rides like Space Mountain. Capture the genuine joy of their first experience on these iconic attractions. A chance to create lasting memories of this special Disney milestone.
+        <v xml:space="preserve">Seeking confident African American women for a beauty brand commercial celebrating natural beauty. Models will participate in an editorial-style shoot, showcasing poise and professionalism. This is a full-day shoot with portfolio-building potential and industry exposure.
 </v>
       </c>
       <c r="E100" t="str">
-        <v>1 - 80</v>
+        <v>30 - 100</v>
       </c>
       <c r="F100" t="str">
-        <v>Any</v>
+        <v>Female</v>
       </c>
       <c r="G100" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672926/edit</v>
+        <v>https://trm.exploretalent.com/cd/projects/1672559/edit</v>
       </c>
       <c r="H100" t="str">
-        <v>06/13/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="I100" t="str">
-        <v>Los Angeles, California</v>
+        <v>New York, United States</v>
       </c>
       <c r="J100" t="str">
-        <v>https://www.exploretalent.com/auditions/1672926</v>
+        <v>https://www.exploretalent.com/auditions/1672559</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
       <c r="A101">
-        <v>1672735</v>
+        <v>1672950</v>
       </c>
       <c r="B101" t="str">
-        <v>Disney Villains: Unfairly Ever After Commercial Casting Call for Hispanic Families</v>
+        <v>Fashion Campaign Casting</v>
       </c>
       <c r="C101" t="str">
+        <v>1200.00/ event</v>
+      </c>
+      <c r="D101" t="str" xml:space="preserve">
+        <v xml:space="preserve">6397 is casting diverse models of all ages and backgrounds for a dynamic fashion campaign. Shoots include lookbook, e-commerce, and B2B visuals. Seeking individuals who exude elegance, energy, and effortless cool to confidently represent the brand's vision.
+</v>
+      </c>
+      <c r="E101" t="str">
+        <v>0 - 18</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G101" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672950/edit</v>
+      </c>
+      <c r="H101" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="I101" t="str">
+        <v>New York, United States</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://www.exploretalent.com/auditions/1672950</v>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102">
+        <v>1674820</v>
+      </c>
+      <c r="B102" t="str">
+        <v>American Apparel Commercial Casting</v>
+      </c>
+      <c r="C102" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D102" t="str" xml:space="preserve">
+        <v xml:space="preserve">LA casting call for a non-union commercial for an American clothing brand. Seeking diverse male and female talent (18-80) for personality-driven roles showcasing modern, everyday fashion. Must be available for wardrobe fitting and multiple shoot days. Natural, makeup-free submissions encouraged. Female roles include light scripted material.
+</v>
+      </c>
+      <c r="E102" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G102" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674820/edit</v>
+      </c>
+      <c r="H102" t="str">
+        <v>07/26/2025</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Los Angeles</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://www.exploretalent.com/auditions/1674820</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103">
+        <v>1674496</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Lancome Photoshoot Casting Female Models</v>
+      </c>
+      <c r="C103" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lancome is seeking female models (18-80, any ethnicity) for a 3-4 hour photoshoot in New York.
+</v>
+      </c>
+      <c r="E103" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G103" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674496/edit</v>
+      </c>
+      <c r="H103" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="I103" t="str">
+        <v>New York, NY, United States</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://www.exploretalent.com/auditions/1674496</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104">
+        <v>1673948</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Tradespeople Casting for Commercial in New Hampshire</v>
+      </c>
+      <c r="C104" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking skilled plumbers, electricians, carpenters, construction workers, and HVAC technicians for a commercial shoot. Must have real-world experience, a professional attitude, and be comfortable performing light, realistic work on camera while collaborating with the crew.
+</v>
+      </c>
+      <c r="E104" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G104" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673948/edit</v>
+      </c>
+      <c r="H104" t="str">
+        <v>07/11/2025</v>
+      </c>
+      <c r="I104" t="str">
+        <v>New Hampshire</v>
+      </c>
+      <c r="J104" t="str">
+        <v>https://www.exploretalent.com/auditions/1673948</v>
+      </c>
+    </row>
+    <row r="105" xml:space="preserve">
+      <c r="A105">
+        <v>1673643</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Casting Call for Twins in Major TV Series</v>
+      </c>
+      <c r="C105" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Major TV series seeks identical male twins, ages 3-5, to play a featured Jewish son in a background role. Paid opportunity for on-set experience. Must be available for filming between June 16-18, camera-ready, and cooperative, following directions from staff and guardians.
+</v>
+      </c>
+      <c r="E105" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G105" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673643/edit</v>
+      </c>
+      <c r="H105" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Los Angeles</v>
+      </c>
+      <c r="J105" t="str">
+        <v>https://www.exploretalent.com/auditions/1673643</v>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106">
+        <v>1672308</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Casting Real People for Documentary Series: Life in the City</v>
+      </c>
+      <c r="C106" t="str">
+        <v>1000.00/ event</v>
+      </c>
+      <c r="D106" t="str" xml:space="preserve">
+        <v xml:space="preserve">"Life in the City" seeks real people (21-80, all genders) in NYC, Chicago, Detroit, or Atlanta to share their urban experiences. This unscripted documentary aims to capture authentic stories, break stereotypes, and reflect modern city living. Participants will be filmed in their city this summer.
+</v>
+      </c>
+      <c r="E106" t="str">
+        <v>21 - 80</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G106" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672308/edit</v>
+      </c>
+      <c r="H106" t="str">
+        <v>06/27/2025</v>
+      </c>
+      <c r="I106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J106" t="str">
+        <v>https://www.exploretalent.com/auditions/1672308</v>
+      </c>
+    </row>
+    <row r="107" xml:space="preserve">
+      <c r="A107">
+        <v>1672176</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Global Athletic Brand Live Event Hosts Ushers Greeters</v>
+      </c>
+      <c r="C107" t="str">
+        <v>1000.00/ negotiable</v>
+      </c>
+      <c r="D107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking charismatic, confident Brazilian hosts, ushers, and greeters (ages 18-30) with standout style to represent Brazil's cultural energy at an international athletic brand's event in Los Angeles. They will welcome guests, maintain an energetic atmosphere, and support event flow.
+</v>
+      </c>
+      <c r="E107" t="str">
+        <v>18 - 30</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G107" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672176/edit</v>
+      </c>
+      <c r="H107" t="str">
+        <v>06/29/2025</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Los Angeles, California, United States</v>
+      </c>
+      <c r="J107" t="str">
+        <v>https://www.exploretalent.com/auditions/1672176</v>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108">
+        <v>1674752</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Casting Female Dancers for International Performance Contract</v>
+      </c>
+      <c r="C108" t="str">
+        <v>1000.00/ month</v>
+      </c>
+      <c r="D108" t="str" xml:space="preserve">
+        <v xml:space="preserve">UK/Europe-based female dancers wanted for a 6-month international contract in India. Perform in music videos, film shoots, and weddings. A great opportunity for industry exposure.
+</v>
+      </c>
+      <c r="E108" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G108" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674752/edit</v>
+      </c>
+      <c r="H108" t="str">
+        <v>07/24/2025</v>
+      </c>
+      <c r="I108" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="J108" t="str">
+        <v>https://www.exploretalent.com/auditions/1674752</v>
+      </c>
+    </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109">
+        <v>1674062</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Gaming Company Commercial Casting Call</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D109" t="str" xml:space="preserve">
+        <v xml:space="preserve">A gaming company seeks male talent (20-80) for a non-union commercial. Performers will portray gamers of various ages, interacting with gaming products on camera. Strong non-verbal acting skills and camera presence are essential.
+</v>
+      </c>
+      <c r="E109" t="str">
+        <v>20 - 80</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G109" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674062/edit</v>
+      </c>
+      <c r="H109" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Chicago, Illinois</v>
+      </c>
+      <c r="J109" t="str">
+        <v>https://www.exploretalent.com/auditions/1674062</v>
+      </c>
+    </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110">
+        <v>1674017</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Casting Call for Homeownership &amp; Renovation TV Series</v>
+      </c>
+      <c r="C110" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Docu-series seeks homeowners and first-time buyers with bold personalities to share authentic stories of buying, renovating, or redefining "home." Participants will be filmed this summer, showcasing DIY projects, multigenerational living, or unconventional housing choices. National exposure and expert insights provided.
+</v>
+      </c>
+      <c r="E110" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G110" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674017/edit</v>
+      </c>
+      <c r="H110" t="str">
+        <v>07/13/2025</v>
+      </c>
+      <c r="I110" t="str">
+        <v>United States</v>
+      </c>
+      <c r="J110" t="str">
+        <v>https://www.exploretalent.com/auditions/1674017</v>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111">
+        <v>1673634</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Casting Call for Miming Rappers Commercial</v>
+      </c>
+      <c r="C111" t="str">
+        <v>1000.00/ event</v>
+      </c>
+      <c r="D111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking charismatic male performers (25-80) with strong stage presence for a high-energy commercial. Talent will mime a rap song with confidence, dynamic energy, and consistent performance on a one-day shoot, following creative direction.
+</v>
+      </c>
+      <c r="E111" t="str">
+        <v>25 - 80</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G111" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673634/edit</v>
+      </c>
+      <c r="H111" t="str">
+        <v>07/07/2025</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="J111" t="str">
+        <v>https://www.exploretalent.com/auditions/1673634</v>
+      </c>
+    </row>
+    <row r="112" xml:space="preserve">
+      <c r="A112">
+        <v>1673615</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Casting: Japanese Male for UK Commercial</v>
+      </c>
+      <c r="C112" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D112" t="str" xml:space="preserve">
+        <v xml:space="preserve">Casting call for a Japanese male actor/model with a larger build for a one-day commercial shoot. Seeking a talent with a natural, confident on-camera presence to authentically represent the brand. Prior on-camera experience is a plus.
+</v>
+      </c>
+      <c r="E112" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G112" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673615/edit</v>
+      </c>
+      <c r="H112" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I112" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="J112" t="str">
+        <v>https://www.exploretalent.com/auditions/1673615</v>
+      </c>
+    </row>
+    <row r="113" xml:space="preserve">
+      <c r="A113">
+        <v>1672316</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Retired Couple Needed for Travel Commercial Campaign</v>
+      </c>
+      <c r="C113" t="str">
+        <v>1000.00/ event</v>
+      </c>
+      <c r="D113" t="str" xml:space="preserve">
+        <v xml:space="preserve">A travel-themed commercial seeks an adventurous, real-life couple aged 65-70 to portray the joy of retirement. They'll film lifestyle scenes at home and during a mini-getaway to France. No acting experience needed, just natural chemistry and a love for travel.
+</v>
+      </c>
+      <c r="E113" t="str">
+        <v>65 - 70</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G113" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672316/edit</v>
+      </c>
+      <c r="H113" t="str">
+        <v>06/27/2025</v>
+      </c>
+      <c r="I113" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="J113" t="str">
+        <v>https://www.exploretalent.com/auditions/1672316</v>
+      </c>
+    </row>
+    <row r="114" xml:space="preserve">
+      <c r="A114">
+        <v>1672200</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Hair Models Needed for Premier Orlando Showcase</v>
+      </c>
+      <c r="C114" t="str">
+        <v>1000.00/ day</v>
+      </c>
+      <c r="D114" t="str" xml:space="preserve">
+        <v xml:space="preserve">Curly haircare brand seeks female hair models with Type 3-4 hair for Premier Orlando. Models will have hair styled live on stage with heat tools, representing the brand in demos and booth sessions. Professionalism and full event availability are required.
+</v>
+      </c>
+      <c r="E114" t="str">
+        <v>1 - 80</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G114" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672200/edit</v>
+      </c>
+      <c r="H114" t="str">
+        <v>06/30/2025</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Orlando, Florida</v>
+      </c>
+      <c r="J114" t="str">
+        <v>https://www.exploretalent.com/auditions/1672200</v>
+      </c>
+    </row>
+    <row r="115" xml:space="preserve">
+      <c r="A115">
+        <v>1674078</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Derek Jeter Commercial Casting Baseball Players</v>
+      </c>
+      <c r="C115" t="str">
+        <v>986.80/ day</v>
+      </c>
+      <c r="D115" t="str" xml:space="preserve">
+        <v xml:space="preserve">SAG commercial casting real male baseball players (18-80) with recent/current experience to star alongside Derek Jeter for a major sports betting brand. No acting experience needed. The shoot involves baseball skills, on-set direction, and athletic performance. Overnight calls and full production days possible.
+</v>
+      </c>
+      <c r="E115" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G115" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674078/edit</v>
+      </c>
+      <c r="H115" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Miami</v>
+      </c>
+      <c r="J115" t="str">
+        <v>https://www.exploretalent.com/auditions/1674078</v>
+      </c>
+    </row>
+    <row r="116" xml:space="preserve">
+      <c r="A116">
+        <v>1674348</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Casting Male Talent for Huckberry Campaign</v>
+      </c>
+      <c r="C116" t="str">
+        <v>970.00/ event</v>
+      </c>
+      <c r="D116" t="str" xml:space="preserve">
+        <v xml:space="preserve">Huckberry is casting male talent (18-80) with real, approachable personalities for lifestyle shoots. Ideal candidates are hikers, explorers, or urban creatives with an outdoorsy edge, comfortable on camera in various settings. Outdoor/athletic experience is a plus. Availability for full shoot day(s) required.
+</v>
+      </c>
+      <c r="E116" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G116" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674348/edit</v>
+      </c>
+      <c r="H116" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="I116" t="str">
+        <v>United States</v>
+      </c>
+      <c r="J116" t="str">
+        <v>https://www.exploretalent.com/auditions/1674348</v>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117">
+        <v>1674083</v>
+      </c>
+      <c r="B117" t="str">
+        <v>GEICO Commercial Casting Call for Reliever Roles</v>
+      </c>
+      <c r="C117" t="str">
+        <v>822.30/ day</v>
+      </c>
+      <c r="D117" t="str" xml:space="preserve">
+        <v xml:space="preserve">Comedic actors (25-80, male) with strong improv skills and athletic energy are needed for "Reliever" roles in a sports-themed commercial campaign. Roles involve scripted scenes, potential improv, and possible social media content. Baseball knowledge/athleticism preferred for some. SAG contracts apply; NDA required.
+</v>
+      </c>
+      <c r="E117" t="str">
+        <v>25 - 80</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G117" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674083/edit</v>
+      </c>
+      <c r="H117" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Fredericksburg, Virginia</v>
+      </c>
+      <c r="J117" t="str">
+        <v>https://www.exploretalent.com/auditions/1674083</v>
+      </c>
+    </row>
+    <row r="118" xml:space="preserve">
+      <c r="A118">
+        <v>1674051</v>
+      </c>
+      <c r="B118" t="str">
+        <v>GEICO Commercial Casting Call for Sports Fans</v>
+      </c>
+      <c r="C118" t="str">
+        <v>822.30/ day</v>
+      </c>
+      <c r="D118" t="str" xml:space="preserve">
+        <v xml:space="preserve">Commercial casting seeks comedic, expressive fans (25-80, all ethnicities) for scripted sports scenes filming in Fredericksburg, VA. Roles involve portraying enthusiastic/quirky fans, reacting naturally, and light improv. National exposure possible. Experience preferred, but not required.
+</v>
+      </c>
+      <c r="E118" t="str">
+        <v>25 - 80</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G118" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674051/edit</v>
+      </c>
+      <c r="H118" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Fredericksburg, Virginia</v>
+      </c>
+      <c r="J118" t="str">
+        <v>https://www.exploretalent.com/auditions/1674051</v>
+      </c>
+    </row>
+    <row r="119" xml:space="preserve">
+      <c r="A119">
+        <v>1674050</v>
+      </c>
+      <c r="B119" t="str">
+        <v>GEICO SAG Commercial Casting Call</v>
+      </c>
+      <c r="C119" t="str">
+        <v>822.30/ day</v>
+      </c>
+      <c r="D119" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking a male actor, aged 50-80, for a comedic national commercial. The role is a charming, believable, and seasoned ballpark concession vendor. Must deliver lines with subtle humor, take direction well, and engage dynamically with other talent in a high-exposure setting.
+</v>
+      </c>
+      <c r="E119" t="str">
+        <v>50 - 80</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G119" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674050/edit</v>
+      </c>
+      <c r="H119" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Fredericksburg</v>
+      </c>
+      <c r="J119" t="str">
+        <v>https://www.exploretalent.com/auditions/1674050</v>
+      </c>
+    </row>
+    <row r="120" xml:space="preserve">
+      <c r="A120">
+        <v>1674049</v>
+      </c>
+      <c r="B120" t="str">
+        <v>GEICO Commercial Casting Call for Cleaning Crew</v>
+      </c>
+      <c r="C120" t="str">
+        <v>822.30/ day</v>
+      </c>
+      <c r="D120" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking male background talent (30-80) to play a cleaning crew member in a comedic "Robot Vacuum" segment for a sports-themed commercial. The role involves light action, reactions, and contributing to the humor. Potential for national campaign exposure on social media.
+</v>
+      </c>
+      <c r="E120" t="str">
+        <v>30 - 80</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G120" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674049/edit</v>
+      </c>
+      <c r="H120" t="str">
+        <v>07/12/2025</v>
+      </c>
+      <c r="I120" t="str">
+        <v>United States</v>
+      </c>
+      <c r="J120" t="str">
+        <v>https://www.exploretalent.com/auditions/1674049</v>
+      </c>
+    </row>
+    <row r="121" xml:space="preserve">
+      <c r="A121">
+        <v>1674400</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Fashion Film &amp; Footwear Campaign Casting</v>
+      </c>
+      <c r="C121" t="str">
         <v>800.00/ day</v>
       </c>
-      <c r="D101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Hispanic/Latinx families wanted for a Disney commercial! Participate in a fun, non-speaking B-roll shoot capturing authentic reactions during live stage shows. Create lasting memories and be part of a professional project.
-</v>
-      </c>
-      <c r="E101" t="str">
-        <v>1 - 80</v>
-      </c>
-      <c r="F101" t="str">
-        <v>Any</v>
-      </c>
-      <c r="G101" t="str">
-        <v>https://trm.exploretalent.com/cd/projects/1672735/edit</v>
-      </c>
-      <c r="H101" t="str">
-        <v>06/19/2025</v>
-      </c>
-      <c r="I101" t="str">
-        <v>Orlando, Florida</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://www.exploretalent.com/auditions/1672735</v>
+      <c r="D121" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking vibrant extras, ages 20-35, with runway-ready energy and authentic street style for a fashion film and footwear campaign. Extras will populate runway and lifestyle scenes, showcasing fashion pieces and footwear with natural movement, poise, and professionalism. Direction will be provided on set.
+</v>
+      </c>
+      <c r="E121" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G121" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674400/edit</v>
+      </c>
+      <c r="H121" t="str">
+        <v>07/18/2025</v>
+      </c>
+      <c r="I121" t="str">
+        <v>New York City</v>
+      </c>
+      <c r="J121" t="str">
+        <v>https://www.exploretalent.com/auditions/1674400</v>
+      </c>
+    </row>
+    <row r="122" xml:space="preserve">
+      <c r="A122">
+        <v>1673689</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Casting Call for Netflix's '72 Hours' - Female Nightclub Dancers</v>
+      </c>
+      <c r="C122" t="str">
+        <v>800.00/ hour</v>
+      </c>
+      <c r="D122" t="str" xml:space="preserve">
+        <v xml:space="preserve">"72 Hours" seeks confident, attractive female dancers for high-energy nightclub scenes. Performers should be comfortable in revealing attire and able to deliver bold, expressive performances that bring the nightlife to life on screen.
+</v>
+      </c>
+      <c r="E122" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G122" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673689/edit</v>
+      </c>
+      <c r="H122" t="str">
+        <v>07/07/2025</v>
+      </c>
+      <c r="I122" t="str">
+        <v>New York</v>
+      </c>
+      <c r="J122" t="str">
+        <v>https://www.exploretalent.com/auditions/1673689</v>
+      </c>
+    </row>
+    <row r="123" xml:space="preserve">
+      <c r="A123">
+        <v>1673608</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Adidas Commercial Casting Call for Dancing Janitor</v>
+      </c>
+      <c r="C123" t="str">
+        <v>800.00/ day</v>
+      </c>
+      <c r="D123" t="str" xml:space="preserve">
+        <v xml:space="preserve">Commercial casting seeks a charismatic, physically expressive older male actor (60-80) for a "Dancing Janitor" role. Must perform authentic, reactive movements. Offers fitting payments and usage fees if featured.
+</v>
+      </c>
+      <c r="E123" t="str">
+        <v>60 - 80</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G123" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673608/edit</v>
+      </c>
+      <c r="H123" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Jacksonville</v>
+      </c>
+      <c r="J123" t="str">
+        <v>https://www.exploretalent.com/auditions/1673608</v>
+      </c>
+    </row>
+    <row r="124" xml:space="preserve">
+      <c r="A124">
+        <v>1673352</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Casting Call for Native American Actors in Boston</v>
+      </c>
+      <c r="C124" t="str">
+        <v>800.00/ day</v>
+      </c>
+      <c r="D124" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking a Navajo heritage male actor for a non-union reenactment portraying young Thomas Begay, a Navajo Code Talker, for the Pacific War Museum. The role requires an authentic, respectful performance for a one-day shoot, honoring Begay's legacy and contributing to historical accuracy.
+</v>
+      </c>
+      <c r="E124" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G124" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673352/edit</v>
+      </c>
+      <c r="H124" t="str">
+        <v>07/05/2025</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Boston, Massachusetts</v>
+      </c>
+      <c r="J124" t="str">
+        <v>https://www.exploretalent.com/auditions/1673352</v>
+      </c>
+    </row>
+    <row r="125" xml:space="preserve">
+      <c r="A125">
+        <v>1673298</v>
+      </c>
+      <c r="B125" t="str">
+        <v>A mattress company is casting plus-size men and women for a commercial shoot. This campaign aims to showcase real people with warmth, relatability, and everyday charm. Talent will appear in relaxed, lifestyle-focused scenes that highlight comfort and conn</v>
+      </c>
+      <c r="C125" t="str">
+        <v>800.00/ day</v>
+      </c>
+      <c r="D125" t="str" xml:space="preserve">
+        <v xml:space="preserve">A mattress company is casting plus-size men and women, ages 3-80, for a commercial. All ethnicities are welcome.
+</v>
+      </c>
+      <c r="E125" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G125" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673298/edit</v>
+      </c>
+      <c r="H125" t="str">
+        <v>07/04/2025</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Pennsylvania</v>
+      </c>
+      <c r="J125" t="str">
+        <v>https://www.exploretalent.com/auditions/1673298</v>
+      </c>
+    </row>
+    <row r="126" xml:space="preserve">
+      <c r="A126">
+        <v>1673139</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Athletic Brand Commercial Casting Call</v>
+      </c>
+      <c r="C126" t="str">
+        <v>800.00/ day</v>
+      </c>
+      <c r="D126" t="str" xml:space="preserve">
+        <v xml:space="preserve">A major athletic brand seeks Gen Z models (18-28) for a paid commercial campaign. The shoot requires a wardrobe fitting and a full-day shoot, portraying confident, active lifestyles. Talent must be punctual, professional, and camera-ready. This is a high-visibility brand opportunity.
+</v>
+      </c>
+      <c r="E126" t="str">
+        <v>18 - 28</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G126" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673139/edit</v>
+      </c>
+      <c r="H126" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="I126" t="str">
+        <v>New York</v>
+      </c>
+      <c r="J126" t="str">
+        <v>https://www.exploretalent.com/auditions/1673139</v>
+      </c>
+    </row>
+    <row r="127" xml:space="preserve">
+      <c r="A127">
+        <v>1672165</v>
+      </c>
+      <c r="B127" t="str">
+        <v>NYC Athletic Clothing Brand Commercial Casting Call</v>
+      </c>
+      <c r="C127" t="str">
+        <v>800.00/ negotiable</v>
+      </c>
+      <c r="D127" t="str" xml:space="preserve">
+        <v xml:space="preserve">NYC casting call for an athletic brand commercial seeking diverse men and women, ages 21-80, to portray authentic, everyday people with personality. The campaign celebrates diversity and real-life energy.
+</v>
+      </c>
+      <c r="E127" t="str">
+        <v>21 - 80</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G127" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672165/edit</v>
+      </c>
+      <c r="H127" t="str">
+        <v>06/30/2025</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v>https://www.exploretalent.com/auditions/1672165</v>
+      </c>
+    </row>
+    <row r="128" xml:space="preserve">
+      <c r="A128">
+        <v>1674847</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Male Model Casting for Major Denim Brand Photo Shoot</v>
+      </c>
+      <c r="C128" t="str">
+        <v>775.00/ event</v>
+      </c>
+      <c r="D128" t="str" xml:space="preserve">
+        <v xml:space="preserve">A well-known jean brand seeks a male model for a high-visibility commercial shoot in NYC. The ideal candidate embodies an urban, stylish aesthetic, is confident on camera, and can portray a relaxed, fashion-forward look during a two-hour denim photoshoot.
+</v>
+      </c>
+      <c r="E128" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G128" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1674847/edit</v>
+      </c>
+      <c r="H128" t="str">
+        <v>07/25/2025</v>
+      </c>
+      <c r="I128" t="str">
+        <v>New York, New York</v>
+      </c>
+      <c r="J128" t="str">
+        <v>https://www.exploretalent.com/auditions/1674847</v>
+      </c>
+    </row>
+    <row r="129" xml:space="preserve">
+      <c r="A129">
+        <v>1673693</v>
+      </c>
+      <c r="B129" t="str">
+        <v>DMV Public Utility Video Shoot Casting Call</v>
+      </c>
+      <c r="C129" t="str">
+        <v>750.00/ day</v>
+      </c>
+      <c r="D129" t="str" xml:space="preserve">
+        <v xml:space="preserve">DMV public utility seeks a female lead (20-80) and fifteen extras for an energy efficiency video. The shoot, on a studio cyc, aims to promote sustainable living through relatable storytelling. Extras will be cast from photos.
+</v>
+      </c>
+      <c r="E129" t="str">
+        <v>20 - 80</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G129" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673693/edit</v>
+      </c>
+      <c r="H129" t="str">
+        <v>07/07/2025</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Fairfax, Virginia</v>
+      </c>
+      <c r="J129" t="str">
+        <v>https://www.exploretalent.com/auditions/1673693</v>
+      </c>
+    </row>
+    <row r="130" xml:space="preserve">
+      <c r="A130">
+        <v>1673270</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Vietnamese Actor Casting for Remitly Commercial</v>
+      </c>
+      <c r="C130" t="str">
+        <v>750.00/ event</v>
+      </c>
+      <c r="D130" t="str" xml:space="preserve">
+        <v xml:space="preserve">Remitly seeks a Vietnamese male actor (30-50) for a commercial. The ideal candidate is a warm, energetic, and funny sports enthusiast, like everyone's favorite uncle. On-camera comfort and comedy/improv skills are a plus.
+</v>
+      </c>
+      <c r="E130" t="str">
+        <v>30 - 50</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G130" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673270/edit</v>
+      </c>
+      <c r="H130" t="str">
+        <v>07/04/2025</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Nationwide</v>
+      </c>
+      <c r="J130" t="str">
+        <v>https://www.exploretalent.com/auditions/1673270</v>
+      </c>
+    </row>
+    <row r="131" xml:space="preserve">
+      <c r="A131">
+        <v>1673197</v>
+      </c>
+      <c r="B131" t="str">
+        <v>TDE Music Video Casting Call for Lead Model</v>
+      </c>
+      <c r="C131" t="str">
+        <v>750.00/ day</v>
+      </c>
+      <c r="D131" t="str" xml:space="preserve">
+        <v xml:space="preserve">TDE music video seeks a confident, camera-ready male model/actor (18-26) for a full-day shoot. Immediate booking. Offers significant exposure in a visually stylish, fast-paced production.
+</v>
+      </c>
+      <c r="E131" t="str">
+        <v>18 - 26</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G131" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673197/edit</v>
+      </c>
+      <c r="H131" t="str">
+        <v>07/04/2025</v>
+      </c>
+      <c r="I131" t="str">
+        <v>California</v>
+      </c>
+      <c r="J131" t="str">
+        <v>https://www.exploretalent.com/auditions/1673197</v>
+      </c>
+    </row>
+    <row r="132" xml:space="preserve">
+      <c r="A132">
+        <v>1672304</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Global Athletic Brand Live Event Barber Casting – Brazilian Male Actor Needed</v>
+      </c>
+      <c r="C132" t="str">
+        <v>750.00/ day</v>
+      </c>
+      <c r="D132" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking a charismatic Brazilian male actor (18-50) to play a barber in a live, interactive performance. Requires acting experience, strong presence, and ability to improvise conversations about Brazilian culture and soccer while styling hair. Two-day commitment (event + rehearsal).
+</v>
+      </c>
+      <c r="E132" t="str">
+        <v>18 - 50</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G132" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672304/edit</v>
+      </c>
+      <c r="H132" t="str">
+        <v>06/30/2025</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Los Angeles, California</v>
+      </c>
+      <c r="J132" t="str">
+        <v>https://www.exploretalent.com/auditions/1672304</v>
+      </c>
+    </row>
+    <row r="133" xml:space="preserve">
+      <c r="A133">
+        <v>1672202</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Global Athletic Brand Live Event Teen Barber Customer</v>
+      </c>
+      <c r="C133" t="str">
+        <v>750.00/ day</v>
+      </c>
+      <c r="D133" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking a Brazilian teen male (18-22) for a live barbershop scene in LA, promoting a global athletic brand. The role requires unscripted conversation about soccer and Brazilian culture while getting a haircut, reflecting street style and cultural pride. Rehearsal attendance is mandatory.
+</v>
+      </c>
+      <c r="E133" t="str">
+        <v>18 - 22</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G133" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672202/edit</v>
+      </c>
+      <c r="H133" t="str">
+        <v>06/29/2025</v>
+      </c>
+      <c r="I133" t="str">
+        <v>California, Los Angeles</v>
+      </c>
+      <c r="J133" t="str">
+        <v>https://www.exploretalent.com/auditions/1672202</v>
+      </c>
+    </row>
+    <row r="134" xml:space="preserve">
+      <c r="A134">
+        <v>1672182</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Global Athletic Brand Live Event Dancer Opportunity</v>
+      </c>
+      <c r="C134" t="str">
+        <v>750.00/ negotiable</v>
+      </c>
+      <c r="D134" t="str" xml:space="preserve">
+        <v xml:space="preserve">Seeking Brazilian dancers (18-30) skilled in Passinho de funk or similar street styles for a global athletic brand's live event. Dancers will showcase Brazil's culture through choreographed/freestyle routines, embodying energy, confidence, and individuality. Rehearsals required.
+</v>
+      </c>
+      <c r="E134" t="str">
+        <v>18 - 30</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G134" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672182/edit</v>
+      </c>
+      <c r="H134" t="str">
+        <v>06/29/2025</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Los Angeles, California</v>
+      </c>
+      <c r="J134" t="str">
+        <v>https://www.exploretalent.com/auditions/1672182</v>
+      </c>
+    </row>
+    <row r="135" xml:space="preserve">
+      <c r="A135">
+        <v>1672558</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Lifestyle Brand Commercial Casting Call</v>
+      </c>
+      <c r="C135" t="str">
+        <v>700.00/ event</v>
+      </c>
+      <c r="D135" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lifestyle brand seeks a lead high school student for a commercial. Must have strong on-camera presence and comedic timing to portray relatable school-life moments. The role requires delivering lines with personality, collaborating with the team, and availability for two shoot days.
+</v>
+      </c>
+      <c r="E135" t="str">
+        <v>16 - 100</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G135" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672558/edit</v>
+      </c>
+      <c r="H135" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Atlanta, Georgia</v>
+      </c>
+      <c r="J135" t="str">
+        <v>https://www.exploretalent.com/auditions/1672558</v>
+      </c>
+    </row>
+    <row r="136" xml:space="preserve">
+      <c r="A136">
+        <v>1673797</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Athletic Gear Commercial Casting in Miami</v>
+      </c>
+      <c r="C136" t="str">
+        <v>650.00/ day</v>
+      </c>
+      <c r="D136" t="str" xml:space="preserve">
+        <v xml:space="preserve">Miami commercial casting call for athletic gear seeks diverse talent (ages 3-80) for various roles. The shoot will feature dynamic scenes with diner staff, patrons, athletes, and unique personalities. All ethnicities and genders are welcome.
+</v>
+      </c>
+      <c r="E136" t="str">
+        <v>3 - 80</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G136" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673797/edit</v>
+      </c>
+      <c r="H136" t="str">
+        <v>07/10/2025</v>
+      </c>
+      <c r="I136" t="str">
+        <v>Miami</v>
+      </c>
+      <c r="J136" t="str">
+        <v>https://www.exploretalent.com/auditions/1673797</v>
+      </c>
+    </row>
+    <row r="137" xml:space="preserve">
+      <c r="A137">
+        <v>1673341</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Adidas Commercial Casting Call for Young Diner Waitress</v>
+      </c>
+      <c r="C137" t="str">
+        <v>650.00/ day</v>
+      </c>
+      <c r="D137" t="str" xml:space="preserve">
+        <v xml:space="preserve">Adidas commercial seeks a charismatic actress (20-80) to play a sassy, no-nonsense diner waitress. The role requires delivering lines with confidence and attitude in a high-energy diner setting, while effectively taking direction.
+</v>
+      </c>
+      <c r="E137" t="str">
+        <v>20 - 80</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G137" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673341/edit</v>
+      </c>
+      <c r="H137" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Miami</v>
+      </c>
+      <c r="J137" t="str">
+        <v>https://www.exploretalent.com/auditions/1673341</v>
+      </c>
+    </row>
+    <row r="138" xml:space="preserve">
+      <c r="A138">
+        <v>1673337</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Adidas Commercial Casting for NBA Double</v>
+      </c>
+      <c r="C138" t="str">
+        <v>650.00/ day</v>
+      </c>
+      <c r="D138" t="str" xml:space="preserve">
+        <v xml:space="preserve">Adidas seeks an athletic African American male, age 20-80, with real basketball experience to double for an NBA player. Must convincingly perform basketball moves, match a pro physique, take direction well, and be available for a fitting.
+</v>
+      </c>
+      <c r="E138" t="str">
+        <v>20 - 80</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G138" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673337/edit</v>
+      </c>
+      <c r="H138" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Miami</v>
+      </c>
+      <c r="J138" t="str">
+        <v>https://www.exploretalent.com/auditions/1673337</v>
+      </c>
+    </row>
+    <row r="139" xml:space="preserve">
+      <c r="A139">
+        <v>1673332</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Adidas Commercial Casting Call for Comedy Club Waiter</v>
+      </c>
+      <c r="C139" t="str">
+        <v>650.00/ day</v>
+      </c>
+      <c r="D139" t="str" xml:space="preserve">
+        <v xml:space="preserve">A commercial seeks a quick-witted male actor (17-80) to play a charismatic, expressive comedy club waiter. The role requires excellent comedic timing, fast movement, and the ability to deliver punchy reactions in a lively, fast-paced environment.
+</v>
+      </c>
+      <c r="E139" t="str">
+        <v>17 - 80</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Male</v>
+      </c>
+      <c r="G139" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673332/edit</v>
+      </c>
+      <c r="H139" t="str">
+        <v>07/06/2025</v>
+      </c>
+      <c r="I139" t="str">
+        <v>Miami</v>
+      </c>
+      <c r="J139" t="str">
+        <v>https://www.exploretalent.com/auditions/1673332</v>
+      </c>
+    </row>
+    <row r="140" xml:space="preserve">
+      <c r="A140">
+        <v>1672557</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Lifestyle Brand Commercial Casting Call for Students</v>
+      </c>
+      <c r="C140" t="str">
+        <v>600.00/ event</v>
+      </c>
+      <c r="D140" t="str" xml:space="preserve">
+        <v xml:space="preserve">Casting calls are open for diverse teen actors in a lifestyle brand's high school commercial, plus roles for a Miami app commercial. Additional opportunities include an African American actress for a car dealership, a Caucasian mother-daughter duo for a food commercial, and Southeast Asian/Indian actors for a Diwali scene. Tiffany &amp; Co. seeks polished talent.
+</v>
+      </c>
+      <c r="E140" t="str">
+        <v>16 - 19</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G140" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672557/edit</v>
+      </c>
+      <c r="H140" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Atlanta</v>
+      </c>
+      <c r="J140" t="str">
+        <v>https://www.exploretalent.com/auditions/1672557</v>
+      </c>
+    </row>
+    <row r="141" xml:space="preserve">
+      <c r="A141">
+        <v>1673699</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Fisher Price Commercial Casting Real Families</v>
+      </c>
+      <c r="C141" t="str">
+        <v>600.00/ day</v>
+      </c>
+      <c r="D141" t="str" xml:space="preserve">
+        <v xml:space="preserve">Fisher Price seeks real families with babies/toddlers for a non-union commercial celebrating everyday moments. Twins, multi-generational, and diverse families are encouraged to apply. Selected families will film a commercial in Columbus, OH, focused on play and parent-child bonding with toys.
+</v>
+      </c>
+      <c r="E141" t="str">
+        <v>18 - 80</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G141" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1673699/edit</v>
+      </c>
+      <c r="H141" t="str">
+        <v>07/09/2025</v>
+      </c>
+      <c r="I141" t="str">
+        <v>Columbus, Ohio</v>
+      </c>
+      <c r="J141" t="str">
+        <v>https://www.exploretalent.com/auditions/1673699</v>
+      </c>
+    </row>
+    <row r="142" xml:space="preserve">
+      <c r="A142">
+        <v>1672931</v>
+      </c>
+      <c r="B142" t="str">
+        <v>$550 Atlanta Major Newspaper Article Campaign Casting Call for Featured Models</v>
+      </c>
+      <c r="C142" t="str">
+        <v>550.00/ day</v>
+      </c>
+      <c r="D142" t="str" xml:space="preserve">
+        <v xml:space="preserve">Atlanta casting call for female models (18-35) with bold, dyed, or colorful hair for a major editorial campaign with a nationally recognized newspaper. The shoot celebrates eccentric beauty and individuality, offering high visibility in print and digital.
+</v>
+      </c>
+      <c r="E142" t="str">
+        <v>18 - 35</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Female</v>
+      </c>
+      <c r="G142" t="str">
+        <v>https://trm.exploretalent.com/cd/projects/1672931/edit</v>
+      </c>
+      <c r="H142" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Atlanta</v>
+      </c>
+      <c r="J142" t="str">
+        <v>https://www.exploretalent.com/auditions/1672931</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J142"/>
   </ignoredErrors>
 </worksheet>
 </file>